--- a/IntegrationAPITool/artifacts/requirement_doc/PrincipalPayment.xlsx
+++ b/IntegrationAPITool/artifacts/requirement_doc/PrincipalPayment.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://finastra.sharepoint.com/teams/SOAPtoRESTAPI/Shared Documents/General/2. Loan Principal Payment/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asrivas3\git\remote_agent\IntegrationAPITool\artifacts\requirement_doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D86E2BD7-83C9-47B4-9846-A4C8290CF782}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3BDE34D-1200-4507-9D75-B359EF397C9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="450" firstSheet="1" activeTab="7" xr2:uid="{8CA9F380-F4A4-46F0-8E8E-A76D9066CD93}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="450" firstSheet="1" activeTab="8" xr2:uid="{8CA9F380-F4A4-46F0-8E8E-A76D9066CD93}"/>
   </bookViews>
   <sheets>
     <sheet name="Index" sheetId="37" r:id="rId1"/>
@@ -26,13 +26,13 @@
     <sheet name="Loan Change Transaction" sheetId="31" state="hidden" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Create!$A$6:$Q$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Create!$A$7:$Q$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Loan Change Transaction'!$A$8:$N$137</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Update!$I$1:$I$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Update!$I$1:$I$28</definedName>
     <definedName name="_Hlk86385617" localSheetId="6">Delete!#REF!</definedName>
     <definedName name="_Hlk86385617" localSheetId="10">'Loan Change Transaction'!#REF!</definedName>
-    <definedName name="_Toc139059209" localSheetId="2">Create!$B$22</definedName>
-    <definedName name="_Toc139059209" localSheetId="4">Update!$B$23</definedName>
+    <definedName name="_Toc139059209" localSheetId="2">Create!$B$23</definedName>
+    <definedName name="_Toc139059209" localSheetId="4">Update!$B$24</definedName>
     <definedName name="_Toc81484211" localSheetId="9">OutOfScope!$A$31</definedName>
     <definedName name="_Toc81484212" localSheetId="9">OutOfScope!$A$32</definedName>
     <definedName name="_Toc81484213" localSheetId="9">OutOfScope!$A$33</definedName>
@@ -54,9 +54,9 @@
     <definedName name="feePaidByProfileType3256" localSheetId="10">'Loan Change Transaction'!#REF!</definedName>
     <definedName name="feePaidByServicingGroupAlias3256" localSheetId="6">Delete!#REF!</definedName>
     <definedName name="feePaidByServicingGroupAlias3256" localSheetId="10">'Loan Change Transaction'!#REF!</definedName>
-    <definedName name="GA7610_2" localSheetId="2">Create!$F$16</definedName>
+    <definedName name="GA7610_2" localSheetId="2">Create!$F$17</definedName>
     <definedName name="GA7610_2" localSheetId="4">Update!#REF!</definedName>
-    <definedName name="GA7610_3" localSheetId="2">Create!$F$17</definedName>
+    <definedName name="GA7610_3" localSheetId="2">Create!$F$18</definedName>
     <definedName name="GA7610_3" localSheetId="4">Update!#REF!</definedName>
     <definedName name="nonCashPrincipalPaydown1" localSheetId="2">OutOfScope!$F$15</definedName>
     <definedName name="nonCashPrincipalPaydown1" localSheetId="4">Update!#REF!</definedName>
@@ -64,7 +64,7 @@
     <definedName name="originalExpiryDate3256" localSheetId="10">'Loan Change Transaction'!#REF!</definedName>
     <definedName name="ProfTypeUpd3465" localSheetId="6">Delete!#REF!</definedName>
     <definedName name="ProfTypeUpd3465" localSheetId="10">'Loan Change Transaction'!#REF!</definedName>
-    <definedName name="transactionDate1" localSheetId="2">Create!$F$15</definedName>
+    <definedName name="transactionDate1" localSheetId="2">Create!$F$16</definedName>
     <definedName name="transactionDate1" localSheetId="4">Update!#REF!</definedName>
     <definedName name="useDistributionList3256" localSheetId="6">Delete!#REF!</definedName>
     <definedName name="useDistributionList3256" localSheetId="10">'Loan Change Transaction'!#REF!</definedName>
@@ -112,7 +112,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2711" uniqueCount="784">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2719" uniqueCount="786">
   <si>
     <t>Sl. No.</t>
   </si>
@@ -2943,6 +2943,12 @@
   </si>
   <si>
     <t>Draft Search call attributes updated</t>
+  </si>
+  <si>
+    <t>ENTITY_NAME</t>
+  </si>
+  <si>
+    <t>LoanPrincipalPayment</t>
   </si>
 </sst>
 </file>
@@ -3339,7 +3345,7 @@
     <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -3481,17 +3487,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3502,9 +3521,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3514,14 +3530,8 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3532,18 +3542,9 @@
     <xf numFmtId="0" fontId="15" fillId="6" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -3571,6 +3572,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -3820,9 +3827,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3860,7 +3867,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -3966,7 +3973,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4108,7 +4115,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -4117,17 +4124,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB31404B-DF48-4962-9CC3-4DEB2DFA7F7B}">
   <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="45.44140625" customWidth="1"/>
-    <col min="4" max="4" width="107.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5546875" customWidth="1"/>
-    <col min="6" max="6" width="32.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.42578125" customWidth="1"/>
+    <col min="4" max="4" width="107.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" customWidth="1"/>
+    <col min="6" max="6" width="32.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -4147,7 +4154,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="17">
         <v>1</v>
       </c>
@@ -4160,7 +4167,7 @@
       <c r="D2" s="16"/>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" spans="1:6" s="24" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="17">
         <f>A2+1</f>
         <v>2</v>
@@ -4174,7 +4181,7 @@
       <c r="D3" s="16"/>
       <c r="E3" s="23"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="17">
         <f t="shared" ref="A4:A7" si="0">A3+1</f>
         <v>3</v>
@@ -4188,7 +4195,7 @@
       <c r="D4" s="16"/>
       <c r="E4" s="2"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="17">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -4202,7 +4209,7 @@
       <c r="D5" s="16"/>
       <c r="E5" s="2"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="17">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -4218,7 +4225,7 @@
       </c>
       <c r="E6" s="2"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="17">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -4249,40 +4256,40 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2E55C95-9B5A-4C8F-948D-85E489C1FBD4}">
   <dimension ref="A1:R38"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="1"/>
+    <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="25" style="1" customWidth="1"/>
-    <col min="3" max="4" width="9.109375" style="1"/>
-    <col min="5" max="6" width="29.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.109375" style="1"/>
-    <col min="8" max="8" width="64.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="44.88671875" style="1" customWidth="1"/>
+    <col min="3" max="4" width="9.140625" style="1"/>
+    <col min="5" max="6" width="29.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" style="1"/>
+    <col min="8" max="8" width="64.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="44.85546875" style="1" customWidth="1"/>
     <col min="10" max="10" width="13" style="1" customWidth="1"/>
-    <col min="11" max="11" width="11.109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="18.44140625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="11.140625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="18.42578125" style="1" customWidth="1"/>
     <col min="13" max="13" width="20" style="1" customWidth="1"/>
-    <col min="14" max="14" width="18.6640625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="9.109375" style="1"/>
-    <col min="16" max="16" width="46.88671875" style="1" customWidth="1"/>
-    <col min="17" max="17" width="9.109375" style="1"/>
-    <col min="18" max="18" width="41.88671875" style="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.109375" style="1"/>
+    <col min="14" max="14" width="18.7109375" style="1" customWidth="1"/>
+    <col min="15" max="15" width="9.140625" style="1"/>
+    <col min="16" max="16" width="46.85546875" style="1" customWidth="1"/>
+    <col min="17" max="17" width="9.140625" style="1"/>
+    <col min="18" max="18" width="41.85546875" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="88" t="s">
+    <row r="1" spans="1:18" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A1" s="85" t="s">
         <v>340</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
-      <c r="H1" s="88"/>
-    </row>
-    <row r="2" spans="1:18" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
+      <c r="H1" s="85"/>
+    </row>
+    <row r="2" spans="1:18" ht="120" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>43</v>
       </c>
@@ -4311,7 +4318,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="144" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" ht="165" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -4334,7 +4341,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="16" cm="1">
         <f t="array" aca="1" ref="A4" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>2</v>
@@ -4356,7 +4363,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="16" cm="1">
         <f t="array" aca="1" ref="A5" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>3</v>
@@ -4380,7 +4387,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="16" cm="1">
         <f t="array" aca="1" ref="A6" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>4</v>
@@ -4402,7 +4409,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" ht="225" x14ac:dyDescent="0.25">
       <c r="A7" s="16" cm="1">
         <f t="array" aca="1" ref="A7" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>5</v>
@@ -4426,7 +4433,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="16" cm="1">
         <f t="array" aca="1" ref="A8" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>6</v>
@@ -4448,7 +4455,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="16" cm="1">
         <f t="array" aca="1" ref="A9" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>7</v>
@@ -4470,43 +4477,43 @@
         <v>346</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="88" t="s">
+    <row r="10" spans="1:18" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A10" s="85" t="s">
         <v>355</v>
       </c>
-      <c r="B10" s="88"/>
-      <c r="C10" s="88"/>
-      <c r="D10" s="88"/>
-      <c r="E10" s="88"/>
-      <c r="F10" s="88"/>
-      <c r="G10" s="88"/>
-      <c r="H10" s="88"/>
-      <c r="I10" s="88"/>
-      <c r="J10" s="88"/>
-      <c r="K10" s="88"/>
-      <c r="L10" s="88"/>
-      <c r="M10" s="88"/>
-      <c r="N10" s="88"/>
-    </row>
-    <row r="11" spans="1:18" ht="18" x14ac:dyDescent="0.35">
-      <c r="A11" s="89" t="s">
+      <c r="B10" s="85"/>
+      <c r="C10" s="85"/>
+      <c r="D10" s="85"/>
+      <c r="E10" s="85"/>
+      <c r="F10" s="85"/>
+      <c r="G10" s="85"/>
+      <c r="H10" s="85"/>
+      <c r="I10" s="85"/>
+      <c r="J10" s="85"/>
+      <c r="K10" s="85"/>
+      <c r="L10" s="85"/>
+      <c r="M10" s="85"/>
+      <c r="N10" s="85"/>
+    </row>
+    <row r="11" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A11" s="86" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="89"/>
-      <c r="C11" s="89"/>
-      <c r="D11" s="89"/>
-      <c r="E11" s="89"/>
-      <c r="F11" s="89"/>
-      <c r="G11" s="89"/>
-      <c r="H11" s="89"/>
-      <c r="I11" s="89"/>
-      <c r="J11" s="89"/>
-      <c r="K11" s="89"/>
-      <c r="L11" s="89"/>
-      <c r="M11" s="89"/>
-      <c r="N11" s="89"/>
-    </row>
-    <row r="12" spans="1:18" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="B11" s="86"/>
+      <c r="C11" s="86"/>
+      <c r="D11" s="86"/>
+      <c r="E11" s="86"/>
+      <c r="F11" s="86"/>
+      <c r="G11" s="86"/>
+      <c r="H11" s="86"/>
+      <c r="I11" s="86"/>
+      <c r="J11" s="86"/>
+      <c r="K11" s="86"/>
+      <c r="L11" s="86"/>
+      <c r="M11" s="86"/>
+      <c r="N11" s="86"/>
+    </row>
+    <row r="12" spans="1:18" ht="120" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>43</v>
       </c>
@@ -4562,7 +4569,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="50">
         <v>1</v>
       </c>
@@ -4594,7 +4601,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" ht="195" x14ac:dyDescent="0.25">
       <c r="A14" s="16" cm="1">
         <f t="array" aca="1" ref="A14" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>2</v>
@@ -4629,7 +4636,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" ht="225" x14ac:dyDescent="0.25">
       <c r="A15" s="16" cm="1">
         <f t="array" aca="1" ref="A15" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>3</v>
@@ -4664,7 +4671,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="144" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" ht="165" x14ac:dyDescent="0.25">
       <c r="A16" s="16" cm="1">
         <f t="array" aca="1" ref="A16" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>4</v>
@@ -4699,7 +4706,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="16" cm="1">
         <f t="array" aca="1" ref="A17" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>5</v>
@@ -4738,7 +4745,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="16" cm="1">
         <f t="array" aca="1" ref="A18" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>6</v>
@@ -4775,7 +4782,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="144" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" ht="150" x14ac:dyDescent="0.25">
       <c r="A19" s="16" cm="1">
         <f t="array" aca="1" ref="A19" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>7</v>
@@ -4810,43 +4817,43 @@
         <v>362</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="88" t="s">
+    <row r="20" spans="1:18" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A20" s="85" t="s">
         <v>363</v>
       </c>
-      <c r="B20" s="88"/>
-      <c r="C20" s="88"/>
-      <c r="D20" s="88"/>
-      <c r="E20" s="88"/>
-      <c r="F20" s="88"/>
-      <c r="G20" s="88"/>
-      <c r="H20" s="88"/>
-      <c r="I20" s="88"/>
-      <c r="J20" s="88"/>
-      <c r="K20" s="88"/>
-      <c r="L20" s="88"/>
-      <c r="M20" s="88"/>
-      <c r="N20" s="88"/>
-    </row>
-    <row r="21" spans="1:18" ht="18" x14ac:dyDescent="0.35">
-      <c r="A21" s="89" t="s">
+      <c r="B20" s="85"/>
+      <c r="C20" s="85"/>
+      <c r="D20" s="85"/>
+      <c r="E20" s="85"/>
+      <c r="F20" s="85"/>
+      <c r="G20" s="85"/>
+      <c r="H20" s="85"/>
+      <c r="I20" s="85"/>
+      <c r="J20" s="85"/>
+      <c r="K20" s="85"/>
+      <c r="L20" s="85"/>
+      <c r="M20" s="85"/>
+      <c r="N20" s="85"/>
+    </row>
+    <row r="21" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A21" s="86" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="89"/>
-      <c r="C21" s="89"/>
-      <c r="D21" s="89"/>
-      <c r="E21" s="89"/>
-      <c r="F21" s="89"/>
-      <c r="G21" s="89"/>
-      <c r="H21" s="89"/>
-      <c r="I21" s="89"/>
-      <c r="J21" s="89"/>
-      <c r="K21" s="89"/>
-      <c r="L21" s="89"/>
-      <c r="M21" s="89"/>
-      <c r="N21" s="89"/>
-    </row>
-    <row r="22" spans="1:18" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="B21" s="86"/>
+      <c r="C21" s="86"/>
+      <c r="D21" s="86"/>
+      <c r="E21" s="86"/>
+      <c r="F21" s="86"/>
+      <c r="G21" s="86"/>
+      <c r="H21" s="86"/>
+      <c r="I21" s="86"/>
+      <c r="J21" s="86"/>
+      <c r="K21" s="86"/>
+      <c r="L21" s="86"/>
+      <c r="M21" s="86"/>
+      <c r="N21" s="86"/>
+    </row>
+    <row r="22" spans="1:18" ht="120" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>43</v>
       </c>
@@ -4894,7 +4901,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="144" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" ht="165" x14ac:dyDescent="0.25">
       <c r="A23" s="50">
         <v>1</v>
       </c>
@@ -4926,7 +4933,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="16" cm="1">
         <f t="array" aca="1" ref="A24" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>2</v>
@@ -4957,7 +4964,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" ht="195" x14ac:dyDescent="0.25">
       <c r="A25" s="16" cm="1">
         <f t="array" aca="1" ref="A25" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>3</v>
@@ -4990,7 +4997,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" ht="225" x14ac:dyDescent="0.25">
       <c r="A26" s="16" cm="1">
         <f t="array" aca="1" ref="A26" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>4</v>
@@ -5023,7 +5030,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="16" cm="1">
         <f t="array" aca="1" ref="A27" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>5</v>
@@ -5060,7 +5067,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="16" cm="1">
         <f t="array" aca="1" ref="A28" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>6</v>
@@ -5097,7 +5104,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="288" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" ht="300" x14ac:dyDescent="0.25">
       <c r="A29" s="16" cm="1">
         <f t="array" aca="1" ref="A29" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>7</v>
@@ -5132,91 +5139,91 @@
         <v>362</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="88" t="s">
+    <row r="30" spans="1:18" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A30" s="85" t="s">
         <v>366</v>
       </c>
-      <c r="B30" s="88"/>
-      <c r="C30" s="88"/>
-      <c r="D30" s="88"/>
-      <c r="E30" s="88"/>
-      <c r="F30" s="88"/>
-      <c r="G30" s="88"/>
-      <c r="H30" s="88"/>
-      <c r="I30" s="88"/>
-      <c r="J30" s="88"/>
-      <c r="K30" s="88"/>
-      <c r="L30" s="88"/>
-      <c r="M30" s="88"/>
-      <c r="N30" s="88"/>
+      <c r="B30" s="85"/>
+      <c r="C30" s="85"/>
+      <c r="D30" s="85"/>
+      <c r="E30" s="85"/>
+      <c r="F30" s="85"/>
+      <c r="G30" s="85"/>
+      <c r="H30" s="85"/>
+      <c r="I30" s="85"/>
+      <c r="J30" s="85"/>
+      <c r="K30" s="85"/>
+      <c r="L30" s="85"/>
+      <c r="M30" s="85"/>
+      <c r="N30" s="85"/>
       <c r="O30" s="55"/>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A31" s="87" t="s">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A31" s="84" t="s">
         <v>367</v>
       </c>
-      <c r="B31" s="87"/>
-      <c r="C31" s="87"/>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A32" s="90" t="s">
+      <c r="B31" s="84"/>
+      <c r="C31" s="84"/>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A32" s="87" t="s">
         <v>368</v>
       </c>
-      <c r="B32" s="90"/>
-      <c r="C32" s="90"/>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="90" t="s">
+      <c r="B32" s="87"/>
+      <c r="C32" s="87"/>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A33" s="87" t="s">
         <v>369</v>
       </c>
-      <c r="B33" s="90"/>
-      <c r="C33" s="90"/>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="90" t="s">
+      <c r="B33" s="87"/>
+      <c r="C33" s="87"/>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A34" s="87" t="s">
         <v>370</v>
       </c>
-      <c r="B34" s="90"/>
-      <c r="C34" s="90"/>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="90" t="s">
+      <c r="B34" s="87"/>
+      <c r="C34" s="87"/>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A35" s="87" t="s">
         <v>371</v>
       </c>
-      <c r="B35" s="90"/>
-      <c r="C35" s="90"/>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="90" t="s">
+      <c r="B35" s="87"/>
+      <c r="C35" s="87"/>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A36" s="87" t="s">
         <v>372</v>
       </c>
-      <c r="B36" s="90"/>
-      <c r="C36" s="90"/>
-    </row>
-    <row r="37" spans="1:14" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="88" t="s">
+      <c r="B36" s="87"/>
+      <c r="C36" s="87"/>
+    </row>
+    <row r="37" spans="1:14" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A37" s="85" t="s">
         <v>373</v>
       </c>
-      <c r="B37" s="88"/>
-      <c r="C37" s="88"/>
-      <c r="D37" s="88"/>
-      <c r="E37" s="88"/>
-      <c r="F37" s="88"/>
-      <c r="G37" s="88"/>
-      <c r="H37" s="88"/>
-      <c r="I37" s="88"/>
-      <c r="J37" s="88"/>
-      <c r="K37" s="88"/>
-      <c r="L37" s="88"/>
-      <c r="M37" s="88"/>
-      <c r="N37" s="88"/>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="87" t="s">
+      <c r="B37" s="85"/>
+      <c r="C37" s="85"/>
+      <c r="D37" s="85"/>
+      <c r="E37" s="85"/>
+      <c r="F37" s="85"/>
+      <c r="G37" s="85"/>
+      <c r="H37" s="85"/>
+      <c r="I37" s="85"/>
+      <c r="J37" s="85"/>
+      <c r="K37" s="85"/>
+      <c r="L37" s="85"/>
+      <c r="M37" s="85"/>
+      <c r="N37" s="85"/>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A38" s="84" t="s">
         <v>372</v>
       </c>
-      <c r="B38" s="87"/>
-      <c r="C38" s="87"/>
+      <c r="B38" s="84"/>
+      <c r="C38" s="84"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -5243,161 +5250,161 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5AA9480-FECE-4D77-AD12-36E3BA69C1AC}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:P260"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="4"/>
-    <col min="2" max="2" width="32.5546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" style="8" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="4"/>
+    <col min="2" max="2" width="32.5703125" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" style="8" customWidth="1"/>
     <col min="4" max="4" width="13" style="8" customWidth="1"/>
     <col min="5" max="5" width="38" customWidth="1"/>
-    <col min="6" max="6" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.5546875" customWidth="1"/>
-    <col min="8" max="8" width="50.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.88671875" customWidth="1"/>
-    <col min="11" max="11" width="8.44140625" customWidth="1"/>
-    <col min="13" max="13" width="21.5546875" customWidth="1"/>
-    <col min="14" max="15" width="8.88671875" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.5703125" customWidth="1"/>
+    <col min="8" max="8" width="50.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.85546875" customWidth="1"/>
+    <col min="11" max="11" width="8.42578125" customWidth="1"/>
+    <col min="13" max="13" width="21.5703125" customWidth="1"/>
+    <col min="14" max="15" width="8.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="75" t="s">
+    <row r="1" spans="1:16" s="4" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="77" t="s">
         <v>374</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-      <c r="H1" s="75"/>
-      <c r="I1" s="75"/>
-      <c r="J1" s="75"/>
-      <c r="K1" s="75"/>
-      <c r="L1" s="75"/>
-      <c r="M1" s="75"/>
-      <c r="N1" s="75"/>
-      <c r="O1" s="75"/>
-      <c r="P1" s="75"/>
-    </row>
-    <row r="2" spans="1:16" ht="18" x14ac:dyDescent="0.35">
-      <c r="A2" s="76" t="s">
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
+      <c r="L1" s="77"/>
+      <c r="M1" s="77"/>
+      <c r="N1" s="77"/>
+      <c r="O1" s="77"/>
+      <c r="P1" s="77"/>
+    </row>
+    <row r="2" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A2" s="66" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="76"/>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
-      <c r="K2" s="76"/>
-      <c r="L2" s="76"/>
-      <c r="M2" s="76"/>
-      <c r="N2" s="76"/>
-      <c r="O2" s="76"/>
-      <c r="P2" s="76"/>
-    </row>
-    <row r="3" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="92" t="s">
+      <c r="B2" s="66"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="66"/>
+      <c r="I2" s="66"/>
+      <c r="J2" s="66"/>
+      <c r="K2" s="66"/>
+      <c r="L2" s="66"/>
+      <c r="M2" s="66"/>
+      <c r="N2" s="66"/>
+      <c r="O2" s="66"/>
+      <c r="P2" s="66"/>
+    </row>
+    <row r="3" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="89" t="s">
         <v>375</v>
       </c>
-      <c r="B3" s="93"/>
-      <c r="C3" s="93"/>
-      <c r="D3" s="93"/>
-      <c r="E3" s="93"/>
-      <c r="F3" s="93"/>
-      <c r="G3" s="93"/>
-      <c r="H3" s="93"/>
-      <c r="I3" s="93"/>
-      <c r="J3" s="93"/>
-      <c r="K3" s="93"/>
-      <c r="L3" s="93"/>
-      <c r="M3" s="93"/>
-      <c r="N3" s="93"/>
-      <c r="O3" s="93"/>
-      <c r="P3" s="93"/>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A4" s="94" t="s">
+      <c r="B3" s="90"/>
+      <c r="C3" s="90"/>
+      <c r="D3" s="90"/>
+      <c r="E3" s="90"/>
+      <c r="F3" s="90"/>
+      <c r="G3" s="90"/>
+      <c r="H3" s="90"/>
+      <c r="I3" s="90"/>
+      <c r="J3" s="90"/>
+      <c r="K3" s="90"/>
+      <c r="L3" s="90"/>
+      <c r="M3" s="90"/>
+      <c r="N3" s="90"/>
+      <c r="O3" s="90"/>
+      <c r="P3" s="90"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="91" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="95"/>
-      <c r="C4" s="95"/>
-      <c r="D4" s="95"/>
-      <c r="E4" s="95"/>
-      <c r="F4" s="95"/>
-      <c r="G4" s="95"/>
-      <c r="H4" s="95"/>
-      <c r="I4" s="95"/>
-      <c r="J4" s="95"/>
-      <c r="K4" s="95"/>
-      <c r="L4" s="95"/>
-      <c r="M4" s="95"/>
-      <c r="N4" s="95"/>
-      <c r="O4" s="95"/>
-      <c r="P4" s="95"/>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A5" s="94" t="s">
+      <c r="B4" s="92"/>
+      <c r="C4" s="92"/>
+      <c r="D4" s="92"/>
+      <c r="E4" s="92"/>
+      <c r="F4" s="92"/>
+      <c r="G4" s="92"/>
+      <c r="H4" s="92"/>
+      <c r="I4" s="92"/>
+      <c r="J4" s="92"/>
+      <c r="K4" s="92"/>
+      <c r="L4" s="92"/>
+      <c r="M4" s="92"/>
+      <c r="N4" s="92"/>
+      <c r="O4" s="92"/>
+      <c r="P4" s="92"/>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="91" t="s">
         <v>376</v>
       </c>
-      <c r="B5" s="95"/>
-      <c r="C5" s="95"/>
-      <c r="D5" s="95"/>
-      <c r="E5" s="95"/>
-      <c r="F5" s="95"/>
-      <c r="G5" s="95"/>
-      <c r="H5" s="95"/>
-      <c r="I5" s="95"/>
-      <c r="J5" s="95"/>
-      <c r="K5" s="95"/>
-      <c r="L5" s="95"/>
-      <c r="M5" s="95"/>
-      <c r="N5" s="95"/>
-      <c r="O5" s="95"/>
-      <c r="P5" s="95"/>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A6" s="78" t="s">
+      <c r="B5" s="92"/>
+      <c r="C5" s="92"/>
+      <c r="D5" s="92"/>
+      <c r="E5" s="92"/>
+      <c r="F5" s="92"/>
+      <c r="G5" s="92"/>
+      <c r="H5" s="92"/>
+      <c r="I5" s="92"/>
+      <c r="J5" s="92"/>
+      <c r="K5" s="92"/>
+      <c r="L5" s="92"/>
+      <c r="M5" s="92"/>
+      <c r="N5" s="92"/>
+      <c r="O5" s="92"/>
+      <c r="P5" s="92"/>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="67" t="s">
         <v>40</v>
       </c>
-      <c r="B6" s="78"/>
-      <c r="C6" s="78"/>
-      <c r="D6" s="78"/>
-      <c r="E6" s="78"/>
-      <c r="F6" s="78"/>
-      <c r="G6" s="78"/>
-      <c r="H6" s="78"/>
-      <c r="I6" s="78"/>
-      <c r="J6" s="78"/>
-      <c r="K6" s="78"/>
-      <c r="L6" s="78"/>
-      <c r="M6" s="78"/>
-      <c r="N6" s="78"/>
-    </row>
-    <row r="7" spans="1:16" ht="18" x14ac:dyDescent="0.35">
-      <c r="A7" s="91" t="s">
+      <c r="B6" s="67"/>
+      <c r="C6" s="67"/>
+      <c r="D6" s="67"/>
+      <c r="E6" s="67"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="67"/>
+      <c r="H6" s="67"/>
+      <c r="I6" s="67"/>
+      <c r="J6" s="67"/>
+      <c r="K6" s="67"/>
+      <c r="L6" s="67"/>
+      <c r="M6" s="67"/>
+      <c r="N6" s="67"/>
+    </row>
+    <row r="7" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A7" s="88" t="s">
         <v>41</v>
       </c>
-      <c r="B7" s="73"/>
-      <c r="C7" s="73"/>
-      <c r="D7" s="73"/>
-      <c r="E7" s="73"/>
-      <c r="F7" s="73"/>
-      <c r="G7" s="73"/>
-      <c r="H7" s="73"/>
-      <c r="I7" s="73"/>
-      <c r="J7" s="73"/>
-      <c r="K7" s="73"/>
-      <c r="L7" s="73"/>
-      <c r="M7" s="73"/>
-      <c r="N7" s="73"/>
-      <c r="O7" s="73"/>
-      <c r="P7" s="73"/>
-    </row>
-    <row r="8" spans="1:16" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="B7" s="75"/>
+      <c r="C7" s="75"/>
+      <c r="D7" s="75"/>
+      <c r="E7" s="75"/>
+      <c r="F7" s="75"/>
+      <c r="G7" s="75"/>
+      <c r="H7" s="75"/>
+      <c r="I7" s="75"/>
+      <c r="J7" s="75"/>
+      <c r="K7" s="75"/>
+      <c r="L7" s="75"/>
+      <c r="M7" s="75"/>
+      <c r="N7" s="75"/>
+      <c r="O7" s="75"/>
+      <c r="P7" s="75"/>
+    </row>
+    <row r="8" spans="1:16" ht="90" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>43</v>
       </c>
@@ -5447,7 +5454,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="17">
         <v>1</v>
       </c>
@@ -5483,7 +5490,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="17">
         <f>A9+1</f>
         <v>2</v>
@@ -5518,7 +5525,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="17">
         <f t="shared" ref="A11:A74" si="0">A10+1</f>
         <v>3</v>
@@ -5553,7 +5560,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="17">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -5588,7 +5595,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="17">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -5623,7 +5630,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="17">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -5658,7 +5665,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="17">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -5693,7 +5700,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="17">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -5728,7 +5735,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="17">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -5763,7 +5770,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="17">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -5798,7 +5805,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="17">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -5835,7 +5842,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="17">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -5870,7 +5877,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="17">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -5905,7 +5912,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="17">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -5940,7 +5947,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="17">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -5975,7 +5982,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="17">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -6010,7 +6017,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="17">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -6045,7 +6052,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="17">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -6080,7 +6087,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="17">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -6115,7 +6122,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="17">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -6150,7 +6157,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="17">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -6185,7 +6192,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="17">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -6220,7 +6227,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="17">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -6257,7 +6264,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="17">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -6294,7 +6301,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="17">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -6331,7 +6338,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="17">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -6368,7 +6375,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" s="17">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -6405,7 +6412,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" s="17">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -6442,7 +6449,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" s="17">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -6479,7 +6486,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38" s="17">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -6516,7 +6523,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" s="17">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -6553,7 +6560,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40" s="17">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -6588,7 +6595,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" s="17">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -6625,7 +6632,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42" s="17">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -6662,7 +6669,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43" s="17">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -6699,7 +6706,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44" s="17">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -6736,7 +6743,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45" s="17">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -6773,7 +6780,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A46" s="17">
         <f t="shared" si="0"/>
         <v>38</v>
@@ -6810,7 +6817,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A47" s="17">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -6847,7 +6854,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A48" s="17">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -6884,7 +6891,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49" s="17">
         <f t="shared" si="0"/>
         <v>41</v>
@@ -6919,7 +6926,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50" s="17">
         <f t="shared" si="0"/>
         <v>42</v>
@@ -6956,7 +6963,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A51" s="17">
         <f t="shared" si="0"/>
         <v>43</v>
@@ -6991,7 +6998,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A52" s="17">
         <f t="shared" si="0"/>
         <v>44</v>
@@ -7028,7 +7035,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A53" s="17">
         <f t="shared" si="0"/>
         <v>45</v>
@@ -7065,7 +7072,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A54" s="17">
         <f t="shared" si="0"/>
         <v>46</v>
@@ -7102,7 +7109,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A55" s="17">
         <f t="shared" si="0"/>
         <v>47</v>
@@ -7137,7 +7144,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A56" s="17">
         <f t="shared" si="0"/>
         <v>48</v>
@@ -7172,7 +7179,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A57" s="17">
         <f t="shared" si="0"/>
         <v>49</v>
@@ -7209,7 +7216,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A58" s="17">
         <f t="shared" si="0"/>
         <v>50</v>
@@ -7246,7 +7253,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A59" s="17">
         <f t="shared" si="0"/>
         <v>51</v>
@@ -7283,7 +7290,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A60" s="17">
         <f t="shared" si="0"/>
         <v>52</v>
@@ -7320,7 +7327,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A61" s="17">
         <f t="shared" si="0"/>
         <v>53</v>
@@ -7357,7 +7364,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A62" s="17">
         <f t="shared" si="0"/>
         <v>54</v>
@@ -7394,7 +7401,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A63" s="17">
         <f t="shared" si="0"/>
         <v>55</v>
@@ -7429,7 +7436,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A64" s="17">
         <f t="shared" si="0"/>
         <v>56</v>
@@ -7464,7 +7471,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A65" s="17">
         <f t="shared" si="0"/>
         <v>57</v>
@@ -7499,7 +7506,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A66" s="17">
         <f t="shared" si="0"/>
         <v>58</v>
@@ -7534,7 +7541,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A67" s="17">
         <f t="shared" si="0"/>
         <v>59</v>
@@ -7569,7 +7576,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A68" s="17">
         <f t="shared" si="0"/>
         <v>60</v>
@@ -7604,7 +7611,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A69" s="17">
         <f t="shared" si="0"/>
         <v>61</v>
@@ -7639,7 +7646,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A70" s="17">
         <f t="shared" si="0"/>
         <v>62</v>
@@ -7674,7 +7681,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A71" s="17">
         <f t="shared" si="0"/>
         <v>63</v>
@@ -7709,7 +7716,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A72" s="17">
         <f t="shared" si="0"/>
         <v>64</v>
@@ -7744,7 +7751,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A73" s="17">
         <f t="shared" si="0"/>
         <v>65</v>
@@ -7779,7 +7786,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A74" s="17">
         <f t="shared" si="0"/>
         <v>66</v>
@@ -7814,7 +7821,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A75" s="17">
         <f t="shared" ref="A75:A128" si="1">A74+1</f>
         <v>67</v>
@@ -7849,7 +7856,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A76" s="17">
         <f t="shared" si="1"/>
         <v>68</v>
@@ -7884,7 +7891,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A77" s="17">
         <f t="shared" si="1"/>
         <v>69</v>
@@ -7921,7 +7928,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A78" s="17">
         <f t="shared" si="1"/>
         <v>70</v>
@@ -7956,7 +7963,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A79" s="17">
         <f t="shared" si="1"/>
         <v>71</v>
@@ -7993,7 +8000,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A80" s="17">
         <f t="shared" si="1"/>
         <v>72</v>
@@ -8030,7 +8037,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A81" s="17">
         <f t="shared" si="1"/>
         <v>73</v>
@@ -8065,7 +8072,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A82" s="17">
         <f t="shared" si="1"/>
         <v>74</v>
@@ -8102,7 +8109,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A83" s="17">
         <f t="shared" si="1"/>
         <v>75</v>
@@ -8139,7 +8146,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A84" s="17">
         <f t="shared" si="1"/>
         <v>76</v>
@@ -8176,7 +8183,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A85" s="17">
         <f t="shared" si="1"/>
         <v>77</v>
@@ -8211,7 +8218,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A86" s="17">
         <f t="shared" si="1"/>
         <v>78</v>
@@ -8246,7 +8253,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A87" s="17">
         <f t="shared" si="1"/>
         <v>79</v>
@@ -8281,7 +8288,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A88" s="17">
         <f t="shared" si="1"/>
         <v>80</v>
@@ -8316,7 +8323,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A89" s="17">
         <f t="shared" si="1"/>
         <v>81</v>
@@ -8351,7 +8358,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A90" s="17">
         <f t="shared" si="1"/>
         <v>82</v>
@@ -8386,7 +8393,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A91" s="17">
         <f t="shared" si="1"/>
         <v>83</v>
@@ -8421,7 +8428,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A92" s="17">
         <f t="shared" si="1"/>
         <v>84</v>
@@ -8456,7 +8463,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A93" s="17">
         <f t="shared" si="1"/>
         <v>85</v>
@@ -8493,7 +8500,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A94" s="17">
         <f t="shared" si="1"/>
         <v>86</v>
@@ -8530,7 +8537,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A95" s="17">
         <f t="shared" si="1"/>
         <v>87</v>
@@ -8567,7 +8574,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A96" s="17">
         <f t="shared" si="1"/>
         <v>88</v>
@@ -8602,7 +8609,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A97" s="17">
         <f t="shared" si="1"/>
         <v>89</v>
@@ -8639,7 +8646,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A98" s="17">
         <f t="shared" si="1"/>
         <v>90</v>
@@ -8676,7 +8683,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A99" s="17">
         <f t="shared" si="1"/>
         <v>91</v>
@@ -8711,7 +8718,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A100" s="17">
         <f t="shared" si="1"/>
         <v>92</v>
@@ -8746,7 +8753,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A101" s="17">
         <f t="shared" si="1"/>
         <v>93</v>
@@ -8781,7 +8788,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A102" s="17">
         <f t="shared" si="1"/>
         <v>94</v>
@@ -8818,7 +8825,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A103" s="17">
         <f t="shared" si="1"/>
         <v>95</v>
@@ -8855,7 +8862,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A104" s="17">
         <f t="shared" si="1"/>
         <v>96</v>
@@ -8892,7 +8899,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A105" s="17">
         <f t="shared" si="1"/>
         <v>97</v>
@@ -8925,7 +8932,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A106" s="17">
         <f t="shared" si="1"/>
         <v>98</v>
@@ -8960,7 +8967,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A107" s="17">
         <f t="shared" si="1"/>
         <v>99</v>
@@ -8995,7 +9002,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A108" s="17">
         <f t="shared" si="1"/>
         <v>100</v>
@@ -9030,7 +9037,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A109" s="17">
         <f t="shared" si="1"/>
         <v>101</v>
@@ -9065,7 +9072,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A110" s="17">
         <f t="shared" si="1"/>
         <v>102</v>
@@ -9100,7 +9107,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A111" s="17">
         <f t="shared" si="1"/>
         <v>103</v>
@@ -9135,7 +9142,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A112" s="17">
         <f t="shared" si="1"/>
         <v>104</v>
@@ -9170,7 +9177,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A113" s="17">
         <f t="shared" si="1"/>
         <v>105</v>
@@ -9205,7 +9212,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A114" s="17">
         <f t="shared" si="1"/>
         <v>106</v>
@@ -9240,7 +9247,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A115" s="17">
         <f t="shared" si="1"/>
         <v>107</v>
@@ -9275,7 +9282,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A116" s="17">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -9310,7 +9317,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A117" s="17">
         <f t="shared" si="1"/>
         <v>109</v>
@@ -9347,7 +9354,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A118" s="17">
         <f t="shared" si="1"/>
         <v>110</v>
@@ -9382,7 +9389,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A119" s="17">
         <f t="shared" si="1"/>
         <v>111</v>
@@ -9417,7 +9424,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A120" s="17">
         <f t="shared" si="1"/>
         <v>112</v>
@@ -9452,7 +9459,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A121" s="17">
         <f t="shared" si="1"/>
         <v>113</v>
@@ -9487,7 +9494,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="122" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A122" s="17">
         <f t="shared" si="1"/>
         <v>114</v>
@@ -9522,7 +9529,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="123" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A123" s="17">
         <f t="shared" si="1"/>
         <v>115</v>
@@ -9557,7 +9564,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A124" s="17">
         <f t="shared" si="1"/>
         <v>116</v>
@@ -9592,7 +9599,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="125" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A125" s="17">
         <f t="shared" si="1"/>
         <v>117</v>
@@ -9627,7 +9634,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="126" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A126" s="17">
         <f t="shared" si="1"/>
         <v>118</v>
@@ -9662,7 +9669,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="127" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A127" s="17">
         <f t="shared" si="1"/>
         <v>119</v>
@@ -9697,7 +9704,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="128" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A128" s="17">
         <f t="shared" si="1"/>
         <v>120</v>
@@ -9732,26 +9739,26 @@
         <v>64</v>
       </c>
     </row>
-    <row r="129" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A129" s="76" t="s">
+    <row r="129" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A129" s="66" t="s">
         <v>298</v>
       </c>
-      <c r="B129" s="76"/>
-      <c r="C129" s="76"/>
-      <c r="D129" s="76"/>
-      <c r="E129" s="76"/>
-      <c r="F129" s="76"/>
-      <c r="G129" s="76"/>
-      <c r="H129" s="76"/>
-      <c r="I129" s="76"/>
-      <c r="J129" s="76"/>
-      <c r="K129" s="76"/>
-      <c r="L129" s="76"/>
-      <c r="M129" s="76"/>
-      <c r="N129" s="76"/>
+      <c r="B129" s="66"/>
+      <c r="C129" s="66"/>
+      <c r="D129" s="66"/>
+      <c r="E129" s="66"/>
+      <c r="F129" s="66"/>
+      <c r="G129" s="66"/>
+      <c r="H129" s="66"/>
+      <c r="I129" s="66"/>
+      <c r="J129" s="66"/>
+      <c r="K129" s="66"/>
+      <c r="L129" s="66"/>
+      <c r="M129" s="66"/>
+      <c r="N129" s="66"/>
       <c r="O129" s="19"/>
     </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A130" s="7">
         <v>1</v>
       </c>
@@ -9777,7 +9784,7 @@
       <c r="M130" s="2"/>
       <c r="N130" s="2"/>
     </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A131" s="7">
         <f>A130+1</f>
         <v>2</v>
@@ -9802,7 +9809,7 @@
       <c r="M131" s="2"/>
       <c r="N131" s="2"/>
     </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A132" s="7">
         <f t="shared" ref="A132:A136" si="2">A131+1</f>
         <v>3</v>
@@ -9827,7 +9834,7 @@
       <c r="M132" s="2"/>
       <c r="N132" s="2"/>
     </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A133" s="7">
         <f t="shared" si="2"/>
         <v>4</v>
@@ -9852,7 +9859,7 @@
       <c r="M133" s="2"/>
       <c r="N133" s="2"/>
     </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A134" s="7">
         <f t="shared" si="2"/>
         <v>5</v>
@@ -9877,7 +9884,7 @@
       <c r="M134" s="2"/>
       <c r="N134" s="2"/>
     </row>
-    <row r="135" spans="1:15" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:15" ht="105" x14ac:dyDescent="0.25">
       <c r="A135" s="7">
         <f t="shared" si="2"/>
         <v>6</v>
@@ -9906,7 +9913,7 @@
       </c>
       <c r="N135" s="2"/>
     </row>
-    <row r="136" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A136" s="7">
         <f t="shared" si="2"/>
         <v>7</v>
@@ -9933,17 +9940,17 @@
       <c r="M136" s="2"/>
       <c r="N136" s="2"/>
     </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A137" s="14" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B141" s="8" t="s">
         <v>636</v>
       </c>
     </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
         <v>62</v>
       </c>
@@ -9951,7 +9958,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="143" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A143" s="4" t="s">
         <v>62</v>
       </c>
@@ -9959,7 +9966,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="144" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
         <v>62</v>
       </c>
@@ -9967,7 +9974,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" s="4" t="s">
         <v>62</v>
       </c>
@@ -9975,7 +9982,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
         <v>62</v>
       </c>
@@ -9983,7 +9990,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A147" s="4" t="s">
         <v>62</v>
       </c>
@@ -9991,7 +9998,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
         <v>62</v>
       </c>
@@ -9999,7 +10006,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A149" s="4" t="s">
         <v>62</v>
       </c>
@@ -10007,7 +10014,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
         <v>62</v>
       </c>
@@ -10015,7 +10022,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A151" s="4" t="s">
         <v>62</v>
       </c>
@@ -10023,7 +10030,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
         <v>62</v>
       </c>
@@ -10031,7 +10038,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A153" s="4" t="s">
         <v>62</v>
       </c>
@@ -10039,7 +10046,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
         <v>62</v>
       </c>
@@ -10047,7 +10054,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A155" s="4" t="s">
         <v>62</v>
       </c>
@@ -10055,7 +10062,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
         <v>62</v>
       </c>
@@ -10063,7 +10070,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A157" s="4" t="s">
         <v>62</v>
       </c>
@@ -10071,7 +10078,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
         <v>62</v>
       </c>
@@ -10079,7 +10086,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A159" s="4" t="s">
         <v>62</v>
       </c>
@@ -10087,7 +10094,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
         <v>62</v>
       </c>
@@ -10095,7 +10102,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A161" s="4" t="s">
         <v>62</v>
       </c>
@@ -10103,7 +10110,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
         <v>62</v>
       </c>
@@ -10111,7 +10118,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A163" s="4" t="s">
         <v>62</v>
       </c>
@@ -10119,7 +10126,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
         <v>62</v>
       </c>
@@ -10127,7 +10134,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A165" s="4" t="s">
         <v>62</v>
       </c>
@@ -10135,7 +10142,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
         <v>62</v>
       </c>
@@ -10143,7 +10150,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A167" s="4" t="s">
         <v>62</v>
       </c>
@@ -10151,7 +10158,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
         <v>62</v>
       </c>
@@ -10159,7 +10166,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A169" s="4" t="s">
         <v>62</v>
       </c>
@@ -10167,7 +10174,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
         <v>62</v>
       </c>
@@ -10175,7 +10182,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A171" s="4" t="s">
         <v>62</v>
       </c>
@@ -10183,7 +10190,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
         <v>62</v>
       </c>
@@ -10191,7 +10198,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A173" s="4" t="s">
         <v>62</v>
       </c>
@@ -10199,7 +10206,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
         <v>62</v>
       </c>
@@ -10207,7 +10214,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A175" s="4" t="s">
         <v>62</v>
       </c>
@@ -10215,7 +10222,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
         <v>62</v>
       </c>
@@ -10223,7 +10230,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A177" s="4" t="s">
         <v>62</v>
       </c>
@@ -10231,7 +10238,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
         <v>62</v>
       </c>
@@ -10239,7 +10246,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A179" s="4" t="s">
         <v>62</v>
       </c>
@@ -10247,7 +10254,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
         <v>62</v>
       </c>
@@ -10255,7 +10262,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A181" s="4" t="s">
         <v>62</v>
       </c>
@@ -10263,7 +10270,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
         <v>62</v>
       </c>
@@ -10271,7 +10278,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A183" s="4" t="s">
         <v>62</v>
       </c>
@@ -10279,7 +10286,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
         <v>62</v>
       </c>
@@ -10287,7 +10294,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A185" s="4" t="s">
         <v>62</v>
       </c>
@@ -10295,7 +10302,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
         <v>62</v>
       </c>
@@ -10303,7 +10310,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A187" s="4" t="s">
         <v>62</v>
       </c>
@@ -10311,7 +10318,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
         <v>62</v>
       </c>
@@ -10319,7 +10326,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A189" s="4" t="s">
         <v>62</v>
       </c>
@@ -10327,7 +10334,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
         <v>62</v>
       </c>
@@ -10335,7 +10342,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A191" s="4" t="s">
         <v>62</v>
       </c>
@@ -10343,7 +10350,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
         <v>62</v>
       </c>
@@ -10351,7 +10358,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A193" s="4" t="s">
         <v>62</v>
       </c>
@@ -10359,7 +10366,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
         <v>62</v>
       </c>
@@ -10367,7 +10374,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A195" s="4" t="s">
         <v>62</v>
       </c>
@@ -10375,7 +10382,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
         <v>62</v>
       </c>
@@ -10383,7 +10390,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A197" s="4" t="s">
         <v>62</v>
       </c>
@@ -10391,7 +10398,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
         <v>62</v>
       </c>
@@ -10399,7 +10406,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A199" s="4" t="s">
         <v>62</v>
       </c>
@@ -10407,7 +10414,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
         <v>62</v>
       </c>
@@ -10415,7 +10422,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A201" s="4" t="s">
         <v>62</v>
       </c>
@@ -10423,7 +10430,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
         <v>62</v>
       </c>
@@ -10431,7 +10438,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A203" s="4" t="s">
         <v>62</v>
       </c>
@@ -10439,7 +10446,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
         <v>62</v>
       </c>
@@ -10447,7 +10454,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A205" s="4" t="s">
         <v>62</v>
       </c>
@@ -10455,7 +10462,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="s">
         <v>62</v>
       </c>
@@ -10463,7 +10470,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A207" s="4" t="s">
         <v>62</v>
       </c>
@@ -10471,7 +10478,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A208" s="4" t="s">
         <v>62</v>
       </c>
@@ -10479,7 +10486,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A209" s="4" t="s">
         <v>62</v>
       </c>
@@ -10487,7 +10494,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A210" s="4" t="s">
         <v>62</v>
       </c>
@@ -10495,7 +10502,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A211" s="4" t="s">
         <v>62</v>
       </c>
@@ -10503,7 +10510,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="212" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A212" s="4" t="s">
         <v>62</v>
       </c>
@@ -10511,7 +10518,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="213" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A213" s="4" t="s">
         <v>62</v>
       </c>
@@ -10519,7 +10526,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="214" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A214" s="4" t="s">
         <v>62</v>
       </c>
@@ -10527,7 +10534,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="215" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A215" s="4" t="s">
         <v>62</v>
       </c>
@@ -10535,7 +10542,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="216" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A216" s="4" t="s">
         <v>62</v>
       </c>
@@ -10543,7 +10550,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="217" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A217" s="4" t="s">
         <v>62</v>
       </c>
@@ -10551,7 +10558,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="218" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A218" s="4" t="s">
         <v>62</v>
       </c>
@@ -10559,7 +10566,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="219" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A219" s="4" t="s">
         <v>62</v>
       </c>
@@ -10567,7 +10574,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="220" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A220" s="4" t="s">
         <v>62</v>
       </c>
@@ -10575,7 +10582,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="221" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A221" s="4" t="s">
         <v>62</v>
       </c>
@@ -10583,7 +10590,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="222" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A222" s="4" t="s">
         <v>62</v>
       </c>
@@ -10591,7 +10598,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="223" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A223" s="4" t="s">
         <v>62</v>
       </c>
@@ -10599,7 +10606,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="224" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A224" s="4" t="s">
         <v>62</v>
       </c>
@@ -10607,7 +10614,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="225" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A225" s="4" t="s">
         <v>62</v>
       </c>
@@ -10615,7 +10622,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="226" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A226" s="4" t="s">
         <v>62</v>
       </c>
@@ -10623,7 +10630,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="227" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A227" s="4" t="s">
         <v>62</v>
       </c>
@@ -10631,7 +10638,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="228" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A228" s="4" t="s">
         <v>62</v>
       </c>
@@ -10639,7 +10646,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="229" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A229" s="4" t="s">
         <v>62</v>
       </c>
@@ -10647,7 +10654,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="230" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A230" s="4" t="s">
         <v>62</v>
       </c>
@@ -10655,7 +10662,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="231" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A231" s="4" t="s">
         <v>62</v>
       </c>
@@ -10663,7 +10670,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="232" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A232" s="4" t="s">
         <v>62</v>
       </c>
@@ -10671,7 +10678,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="233" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A233" s="4" t="s">
         <v>62</v>
       </c>
@@ -10679,7 +10686,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="234" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A234" s="4" t="s">
         <v>62</v>
       </c>
@@ -10687,7 +10694,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="235" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A235" s="4" t="s">
         <v>62</v>
       </c>
@@ -10695,7 +10702,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="236" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A236" s="4" t="s">
         <v>62</v>
       </c>
@@ -10703,7 +10710,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="237" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A237" s="4" t="s">
         <v>62</v>
       </c>
@@ -10711,7 +10718,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="238" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A238" s="4" t="s">
         <v>62</v>
       </c>
@@ -10719,7 +10726,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="239" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A239" s="4" t="s">
         <v>62</v>
       </c>
@@ -10727,7 +10734,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="240" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A240" s="4" t="s">
         <v>62</v>
       </c>
@@ -10735,7 +10742,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="241" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A241" s="4" t="s">
         <v>62</v>
       </c>
@@ -10743,7 +10750,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="242" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A242" s="4" t="s">
         <v>62</v>
       </c>
@@ -10751,7 +10758,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="243" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A243" s="4" t="s">
         <v>62</v>
       </c>
@@ -10759,7 +10766,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="244" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A244" s="4" t="s">
         <v>62</v>
       </c>
@@ -10767,7 +10774,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="245" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A245" s="4" t="s">
         <v>62</v>
       </c>
@@ -10775,7 +10782,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="246" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A246" s="4" t="s">
         <v>62</v>
       </c>
@@ -10783,7 +10790,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="247" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A247" s="4" t="s">
         <v>62</v>
       </c>
@@ -10791,7 +10798,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="248" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A248" s="4" t="s">
         <v>62</v>
       </c>
@@ -10799,7 +10806,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="249" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A249" s="4" t="s">
         <v>62</v>
       </c>
@@ -10807,7 +10814,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="250" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A250" s="4" t="s">
         <v>62</v>
       </c>
@@ -10815,7 +10822,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="251" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A251" s="4" t="s">
         <v>62</v>
       </c>
@@ -10823,7 +10830,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="252" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A252" s="4" t="s">
         <v>62</v>
       </c>
@@ -10831,7 +10838,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="253" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A253" s="4" t="s">
         <v>62</v>
       </c>
@@ -10839,7 +10846,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="254" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A254" s="4" t="s">
         <v>62</v>
       </c>
@@ -10847,7 +10854,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="255" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A255" s="4" t="s">
         <v>62</v>
       </c>
@@ -10855,7 +10862,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="256" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A256" s="4" t="s">
         <v>62</v>
       </c>
@@ -10863,7 +10870,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="257" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A257" s="4" t="s">
         <v>62</v>
       </c>
@@ -10871,7 +10878,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="258" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A258" s="4" t="s">
         <v>62</v>
       </c>
@@ -10879,7 +10886,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="259" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A259" s="4" t="s">
         <v>62</v>
       </c>
@@ -10887,7 +10894,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="260" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A260" s="4" t="s">
         <v>62</v>
       </c>
@@ -10919,15 +10926,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39B6A51D-93F3-4E7A-B4CC-C71297F1355F}">
   <dimension ref="A1:E15"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="82" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="36" t="s">
         <v>19</v>
       </c>
@@ -10941,7 +10948,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="62">
         <v>1</v>
       </c>
@@ -10953,7 +10960,7 @@
       </c>
       <c r="D2" s="2"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="20">
         <v>1.1000000000000001</v>
       </c>
@@ -10967,7 +10974,7 @@
         <v>45245</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="25">
         <v>1.2</v>
       </c>
@@ -10982,7 +10989,7 @@
       </c>
       <c r="E4" s="18"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
         <v>27</v>
       </c>
@@ -10991,7 +10998,7 @@
       </c>
       <c r="E5" s="18"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
         <v>28</v>
       </c>
@@ -11000,7 +11007,7 @@
       </c>
       <c r="E6" s="18"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C7" s="57" t="s">
         <v>29</v>
       </c>
@@ -11008,11 +11015,11 @@
         <v>45261</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="69">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="72">
         <v>1.3</v>
       </c>
-      <c r="B8" s="69" t="s">
+      <c r="B8" s="72" t="s">
         <v>30</v>
       </c>
       <c r="C8" s="59" t="s">
@@ -11022,9 +11029,9 @@
         <v>45275</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="70"/>
-      <c r="B9" s="70"/>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="73"/>
+      <c r="B9" s="73"/>
       <c r="C9" s="60" t="s">
         <v>32</v>
       </c>
@@ -11033,9 +11040,9 @@
         <v>45275</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="71"/>
-      <c r="B10" s="71"/>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="74"/>
+      <c r="B10" s="74"/>
       <c r="C10" s="29" t="s">
         <v>33</v>
       </c>
@@ -11044,7 +11051,7 @@
         <v>45275</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="20">
         <v>1.4</v>
       </c>
@@ -11059,7 +11066,7 @@
         <v>45280</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="20">
         <v>1.5</v>
       </c>
@@ -11074,7 +11081,7 @@
         <v>45299</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="22">
         <v>1.6</v>
       </c>
@@ -11088,7 +11095,7 @@
         <v>45307</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="22">
         <v>1.7</v>
       </c>
@@ -11102,17 +11109,17 @@
         <v>45310</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="20">
         <v>1.8</v>
       </c>
       <c r="B15" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="67" t="s">
+      <c r="C15" s="17" t="s">
         <v>783</v>
       </c>
-      <c r="D15" s="68">
+      <c r="D15" s="65">
         <v>45331</v>
       </c>
     </row>
@@ -11128,95 +11135,99 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4562C33-095E-4103-B008-03879D66799D}">
-  <dimension ref="A1:Q26"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:R27"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="51" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="40" customWidth="1"/>
-    <col min="6" max="6" width="50.5546875" customWidth="1"/>
-    <col min="7" max="7" width="13.44140625" customWidth="1"/>
-    <col min="8" max="8" width="6.88671875" customWidth="1"/>
-    <col min="9" max="9" width="61.5546875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="10.88671875" customWidth="1"/>
-    <col min="13" max="13" width="26.88671875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="23.6640625" customWidth="1"/>
+    <col min="6" max="6" width="50.5703125" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" customWidth="1"/>
+    <col min="8" max="8" width="6.85546875" customWidth="1"/>
+    <col min="9" max="9" width="61.5703125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.85546875" customWidth="1"/>
+    <col min="13" max="13" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="75" t="s">
+    <row r="1" spans="1:18" s="4" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="77" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-      <c r="H1" s="75"/>
-      <c r="I1" s="75"/>
-      <c r="J1" s="75"/>
-      <c r="K1" s="75"/>
-      <c r="L1" s="75"/>
-      <c r="M1" s="75"/>
-      <c r="N1" s="75"/>
-    </row>
-    <row r="2" spans="1:17" ht="18" x14ac:dyDescent="0.35">
-      <c r="A2" s="76" t="s">
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
+      <c r="L1" s="77"/>
+      <c r="M1" s="77"/>
+      <c r="N1" s="77"/>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="93" t="s">
+        <v>784</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>785</v>
+      </c>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="94"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="R2" s="20"/>
+    </row>
+    <row r="3" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A3" s="66" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="76"/>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
-      <c r="K2" s="76"/>
-      <c r="L2" s="76"/>
-      <c r="M2" s="76"/>
-      <c r="N2" s="76"/>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A3" s="78" t="s">
+      <c r="B3" s="66"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="66"/>
+      <c r="K3" s="66"/>
+      <c r="L3" s="66"/>
+      <c r="M3" s="66"/>
+      <c r="N3" s="66"/>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" s="67" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="78"/>
-      <c r="C3" s="78"/>
-      <c r="D3" s="78"/>
-      <c r="E3" s="78"/>
-      <c r="F3" s="78"/>
-      <c r="G3" s="78"/>
-      <c r="H3" s="78"/>
-      <c r="I3" s="78"/>
-      <c r="J3" s="78"/>
-      <c r="K3" s="78"/>
-      <c r="L3" s="78"/>
-      <c r="M3" s="78"/>
-      <c r="N3" s="78"/>
-    </row>
-    <row r="4" spans="1:17" ht="18" x14ac:dyDescent="0.35">
-      <c r="A4" s="77" t="s">
+      <c r="B4" s="67"/>
+      <c r="C4" s="67"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="67"/>
+      <c r="J4" s="67"/>
+      <c r="K4" s="67"/>
+      <c r="L4" s="67"/>
+      <c r="M4" s="67"/>
+      <c r="N4" s="67"/>
+    </row>
+    <row r="5" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A5" s="78" t="s">
         <v>41</v>
-      </c>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
-      <c r="K4" s="77"/>
-      <c r="L4" s="77"/>
-      <c r="M4" s="77"/>
-      <c r="N4" s="77"/>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A5" s="78" t="s">
-        <v>42</v>
       </c>
       <c r="B5" s="78"/>
       <c r="C5" s="78"/>
@@ -11231,116 +11242,98 @@
       <c r="L5" s="78"/>
       <c r="M5" s="78"/>
       <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-    </row>
-    <row r="6" spans="1:17" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" s="67" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="67"/>
+      <c r="C6" s="67"/>
+      <c r="D6" s="67"/>
+      <c r="E6" s="67"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="67"/>
+      <c r="H6" s="67"/>
+      <c r="I6" s="67"/>
+      <c r="J6" s="67"/>
+      <c r="K6" s="67"/>
+      <c r="L6" s="67"/>
+      <c r="M6" s="67"/>
+      <c r="N6" s="67"/>
+      <c r="O6" s="67"/>
+    </row>
+    <row r="7" spans="1:18" ht="120" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B7" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C7" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D7" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E7" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F7" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="G7" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H7" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="I7" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="J6" s="5" t="s">
+      <c r="J7" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="K6" s="5" t="s">
+      <c r="K7" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="L6" s="5" t="s">
+      <c r="L7" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="M6" s="5" t="s">
+      <c r="M7" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="N6" s="6" t="s">
+      <c r="N7" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="O6" s="9" t="s">
+      <c r="O7" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="P6" s="9" t="s">
+      <c r="P7" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="Q6" s="9" t="s">
+      <c r="Q7" s="9" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A7" s="2">
+    <row r="8" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
         <v>1</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q7" s="35" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A8" s="16" cm="1">
-        <f t="array" aca="1" ref="A8" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>2</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="F8" s="2" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>62</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="J8" s="2"/>
       <c r="K8" s="2" t="s">
@@ -11357,26 +11350,26 @@
         <v>62</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" ht="90" x14ac:dyDescent="0.25">
       <c r="A9" s="16" cm="1">
         <f t="array" aca="1" ref="A9" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="J9" s="2"/>
       <c r="K9" s="2" t="s">
@@ -11389,31 +11382,35 @@
       <c r="P9" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="Q9" s="35"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q9" s="35" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="16" cm="1">
         <f t="array" aca="1" ref="A10" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="F10" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>64</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
+      <c r="K10" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
@@ -11423,26 +11420,26 @@
       </c>
       <c r="Q10" s="35"/>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="16" cm="1">
         <f t="array" aca="1" ref="A11" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>64</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
@@ -11455,31 +11452,29 @@
       </c>
       <c r="Q11" s="35"/>
     </row>
-    <row r="12" spans="1:17" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="16" cm="1">
         <f t="array" aca="1" ref="A12" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="H12" s="79" t="s">
+      <c r="H12" s="2" t="s">
         <v>64</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="J12" s="2"/>
-      <c r="K12" s="2" t="s">
-        <v>64</v>
-      </c>
+      <c r="K12" s="2"/>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
@@ -11487,28 +11482,28 @@
       <c r="P12" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="Q12" s="35" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" ht="72" x14ac:dyDescent="0.3">
+      <c r="Q12" s="35"/>
+    </row>
+    <row r="13" spans="1:18" ht="150" x14ac:dyDescent="0.25">
       <c r="A13" s="16" cm="1">
         <f t="array" aca="1" ref="A13" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="H13" s="80"/>
+      <c r="H13" s="79" t="s">
+        <v>64</v>
+      </c>
       <c r="I13" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="J13" s="2"/>
       <c r="K13" s="2" t="s">
@@ -11525,27 +11520,29 @@
         <v>62</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A14" s="16" cm="1">
         <f t="array" aca="1" ref="A14" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
       <c r="F14" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="I14" s="3"/>
+        <v>61</v>
+      </c>
+      <c r="H14" s="80"/>
+      <c r="I14" s="3" t="s">
+        <v>77</v>
+      </c>
       <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
+      <c r="K14" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
@@ -11553,29 +11550,29 @@
       <c r="P14" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="Q14" s="35"/>
-    </row>
-    <row r="15" spans="1:17" ht="72" x14ac:dyDescent="0.3">
+      <c r="Q14" s="35" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="16" cm="1">
         <f t="array" aca="1" ref="A15" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="I15" s="3" t="s">
-        <v>80</v>
-      </c>
+      <c r="I15" s="3"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
@@ -11587,53 +11584,49 @@
       </c>
       <c r="Q15" s="35"/>
     </row>
-    <row r="16" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A16" s="16" cm="1">
         <f t="array" aca="1" ref="A16" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
       <c r="F16" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="I16" s="39" t="s">
-        <v>82</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>83</v>
-      </c>
+      <c r="I16" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="J16" s="2"/>
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
       <c r="M16" s="2"/>
-      <c r="N16" s="2" t="s">
-        <v>84</v>
-      </c>
+      <c r="N16" s="2"/>
       <c r="O16" s="2"/>
       <c r="P16" s="2" t="s">
         <v>62</v>
       </c>
       <c r="Q16" s="35"/>
     </row>
-    <row r="17" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="16" cm="1">
         <f t="array" aca="1" ref="A17" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
       <c r="F17" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>61</v>
@@ -11642,7 +11635,7 @@
         <v>64</v>
       </c>
       <c r="I17" s="39" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>83</v>
@@ -11650,69 +11643,71 @@
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
       <c r="M17" s="2"/>
-      <c r="N17" s="2"/>
+      <c r="N17" s="2" t="s">
+        <v>84</v>
+      </c>
       <c r="O17" s="2"/>
       <c r="P17" s="2" t="s">
         <v>62</v>
       </c>
       <c r="Q17" s="35"/>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="16" cm="1">
         <f t="array" aca="1" ref="A18" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
       <c r="F18" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="I18" s="3"/>
+      <c r="I18" s="39" t="s">
+        <v>86</v>
+      </c>
       <c r="J18" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>64</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
       <c r="M18" s="2"/>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q18" s="35"/>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="16" cm="1">
         <f t="array" aca="1" ref="A19" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
       <c r="F19" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>64</v>
       </c>
       <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
+      <c r="J19" s="3" t="s">
+        <v>88</v>
+      </c>
       <c r="K19" s="2" t="s">
         <v>64</v>
       </c>
@@ -11727,128 +11722,129 @@
       </c>
       <c r="Q19" s="35"/>
     </row>
-    <row r="20" spans="1:17" ht="18" x14ac:dyDescent="0.35">
-      <c r="A20" s="72" t="s">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A20" s="16" cm="1">
+        <f t="array" aca="1" ref="A20" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
+        <v>13</v>
+      </c>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q20" s="35"/>
+    </row>
+    <row r="21" spans="1:17" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A21" s="68" t="s">
         <v>90</v>
       </c>
-      <c r="B20" s="73"/>
-      <c r="C20" s="73"/>
-      <c r="D20" s="73"/>
-      <c r="E20" s="73"/>
-      <c r="F20" s="73"/>
-      <c r="G20" s="73"/>
-      <c r="H20" s="73"/>
-      <c r="I20" s="73"/>
-      <c r="J20" s="73"/>
-      <c r="K20" s="73"/>
-      <c r="L20" s="73"/>
-      <c r="M20" s="73"/>
-      <c r="N20" s="74"/>
-    </row>
-    <row r="21" spans="1:17" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A21" s="11" t="s">
+      <c r="B21" s="75"/>
+      <c r="C21" s="75"/>
+      <c r="D21" s="75"/>
+      <c r="E21" s="75"/>
+      <c r="F21" s="75"/>
+      <c r="G21" s="75"/>
+      <c r="H21" s="75"/>
+      <c r="I21" s="75"/>
+      <c r="J21" s="75"/>
+      <c r="K21" s="75"/>
+      <c r="L21" s="75"/>
+      <c r="M21" s="75"/>
+      <c r="N21" s="76"/>
+    </row>
+    <row r="22" spans="1:17" ht="120" x14ac:dyDescent="0.25">
+      <c r="A22" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B22" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C22" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D22" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E22" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="F22" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="G21" s="5" t="s">
+      <c r="G22" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="H21" s="5" t="s">
+      <c r="H22" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="I21" s="5" t="s">
+      <c r="I22" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="J21" s="5" t="s">
+      <c r="J22" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="K21" s="5" t="s">
+      <c r="K22" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="L21" s="6" t="s">
+      <c r="L22" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="M21" s="9" t="s">
+      <c r="M22" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="N21" s="9" t="s">
+      <c r="N22" s="9" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A22" s="17">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A23" s="17">
         <v>1</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G22" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="H22" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
-      <c r="L22" s="2"/>
-      <c r="M22" s="2"/>
-      <c r="N22" s="2"/>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A23" s="16" cm="1">
-        <f t="array" aca="1" ref="A23" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>2</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>91</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D23" s="2"/>
+        <v>64</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>62</v>
+      </c>
       <c r="E23" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="G23" s="12" t="s">
         <v>62</v>
       </c>
       <c r="H23" s="12" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
@@ -11856,20 +11852,20 @@
       <c r="M23" s="2"/>
       <c r="N23" s="2"/>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="16" cm="1">
         <f t="array" aca="1" ref="A24" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>91</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>61</v>
@@ -11878,23 +11874,21 @@
         <v>62</v>
       </c>
       <c r="H24" s="12" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
       <c r="M24" s="2"/>
-      <c r="N24" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="N24" s="2"/>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="16" cm="1">
         <f t="array" aca="1" ref="A25" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>91</v>
@@ -11904,10 +11898,10 @@
       </c>
       <c r="D25" s="2"/>
       <c r="E25" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>99</v>
+        <v>61</v>
       </c>
       <c r="G25" s="12" t="s">
         <v>62</v>
@@ -11916,7 +11910,7 @@
         <v>64</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
@@ -11926,24 +11920,59 @@
         <v>64</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A26" s="14" t="s">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A26" s="16" cm="1">
+        <f t="array" aca="1" ref="A26" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
+        <v>4</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G26" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="H26" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
+      <c r="M26" s="2"/>
+      <c r="N26" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A27" s="14" t="s">
         <v>101</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A6:Q26" xr:uid="{C4562C33-095E-4103-B008-03879D66799D}"/>
+  <autoFilter ref="A7:Q27" xr:uid="{C4562C33-095E-4103-B008-03879D66799D}"/>
   <mergeCells count="7">
-    <mergeCell ref="A20:N20"/>
+    <mergeCell ref="A21:N21"/>
     <mergeCell ref="A1:N1"/>
-    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A3:N3"/>
+    <mergeCell ref="A5:N5"/>
     <mergeCell ref="A4:N4"/>
-    <mergeCell ref="A3:N3"/>
-    <mergeCell ref="A5:O5"/>
-    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="A6:O6"/>
+    <mergeCell ref="H13:H14"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A26" location="Index!A1" display="Back to Index" xr:uid="{507B2FF7-EFED-45E9-8DA9-54388F11BE20}"/>
+    <hyperlink ref="A27" location="Index!A1" display="Back to Index" xr:uid="{507B2FF7-EFED-45E9-8DA9-54388F11BE20}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -11953,16 +11982,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B38C28DD-7D9E-4F69-A545-F0C75896CB2C}">
   <dimension ref="A2:Q92"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="74.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="74.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="36" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="37.6640625" customWidth="1"/>
+    <col min="9" max="9" width="37.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="16">
-        <f ca="1">Create!A19+1</f>
+        <f ca="1">Create!A20+1</f>
         <v>14</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -11990,7 +12019,7 @@
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="16">
         <f t="shared" ref="A3:A34" ca="1" si="0">A2+1</f>
         <v>15</v>
@@ -12020,7 +12049,7 @@
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
     </row>
-    <row r="4" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" ht="90" x14ac:dyDescent="0.25">
       <c r="A4" s="16">
         <f t="shared" ca="1" si="0"/>
         <v>16</v>
@@ -12050,7 +12079,7 @@
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
     </row>
-    <row r="5" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="16">
         <f t="shared" ca="1" si="0"/>
         <v>17</v>
@@ -12080,7 +12109,7 @@
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="16">
         <f t="shared" ca="1" si="0"/>
         <v>18</v>
@@ -12110,7 +12139,7 @@
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="16">
         <f t="shared" ca="1" si="0"/>
         <v>19</v>
@@ -12140,7 +12169,7 @@
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="16">
         <f t="shared" ca="1" si="0"/>
         <v>20</v>
@@ -12170,7 +12199,7 @@
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="16">
         <f t="shared" ca="1" si="0"/>
         <v>21</v>
@@ -12200,7 +12229,7 @@
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="16">
         <f t="shared" ca="1" si="0"/>
         <v>22</v>
@@ -12230,7 +12259,7 @@
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
     </row>
-    <row r="11" spans="1:15" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" ht="150" x14ac:dyDescent="0.25">
       <c r="A11" s="16">
         <f t="shared" ca="1" si="0"/>
         <v>23</v>
@@ -12260,7 +12289,7 @@
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
     </row>
-    <row r="12" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" s="16">
         <f t="shared" ca="1" si="0"/>
         <v>24</v>
@@ -12292,7 +12321,7 @@
       </c>
       <c r="O12" s="2"/>
     </row>
-    <row r="13" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="16">
         <f t="shared" ca="1" si="0"/>
         <v>25</v>
@@ -12324,7 +12353,7 @@
       </c>
       <c r="O13" s="2"/>
     </row>
-    <row r="14" spans="1:15" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" ht="105" x14ac:dyDescent="0.25">
       <c r="A14" s="16">
         <f t="shared" ca="1" si="0"/>
         <v>26</v>
@@ -12356,7 +12385,7 @@
       </c>
       <c r="O14" s="2"/>
     </row>
-    <row r="15" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="16">
         <f t="shared" ca="1" si="0"/>
         <v>27</v>
@@ -12386,7 +12415,7 @@
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="16">
         <f t="shared" ca="1" si="0"/>
         <v>28</v>
@@ -12416,7 +12445,7 @@
       <c r="N16" s="2"/>
       <c r="O16" s="29"/>
     </row>
-    <row r="17" spans="1:15" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" ht="57.75" x14ac:dyDescent="0.25">
       <c r="A17" s="16">
         <f t="shared" ca="1" si="0"/>
         <v>29</v>
@@ -12448,7 +12477,7 @@
       <c r="N17" s="2"/>
       <c r="O17" s="29"/>
     </row>
-    <row r="18" spans="1:15" ht="39" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" ht="39.75" x14ac:dyDescent="0.25">
       <c r="A18" s="16">
         <f t="shared" ca="1" si="0"/>
         <v>30</v>
@@ -12478,7 +12507,7 @@
       <c r="N18" s="2"/>
       <c r="O18" s="29"/>
     </row>
-    <row r="19" spans="1:15" ht="147" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" ht="159.75" x14ac:dyDescent="0.25">
       <c r="A19" s="16">
         <f t="shared" ca="1" si="0"/>
         <v>31</v>
@@ -12508,7 +12537,7 @@
       <c r="N19" s="2"/>
       <c r="O19" s="29"/>
     </row>
-    <row r="20" spans="1:15" ht="259.2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" ht="315" x14ac:dyDescent="0.25">
       <c r="A20" s="16">
         <f t="shared" ca="1" si="0"/>
         <v>32</v>
@@ -12538,7 +12567,7 @@
       <c r="N20" s="2"/>
       <c r="O20" s="29"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="16">
         <f t="shared" ca="1" si="0"/>
         <v>33</v>
@@ -12570,7 +12599,7 @@
       <c r="N21" s="2"/>
       <c r="O21" s="29"/>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="16">
         <f t="shared" ca="1" si="0"/>
         <v>34</v>
@@ -12602,7 +12631,7 @@
       <c r="N22" s="2"/>
       <c r="O22" s="29"/>
     </row>
-    <row r="23" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A23" s="16">
         <f t="shared" ca="1" si="0"/>
         <v>35</v>
@@ -12636,7 +12665,7 @@
       </c>
       <c r="O23" s="29"/>
     </row>
-    <row r="24" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="16">
         <f t="shared" ca="1" si="0"/>
         <v>36</v>
@@ -12668,7 +12697,7 @@
       <c r="N24" s="2"/>
       <c r="O24" s="29"/>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="16">
         <f t="shared" ca="1" si="0"/>
         <v>37</v>
@@ -12698,7 +12727,7 @@
       <c r="N25" s="2"/>
       <c r="O25" s="29"/>
     </row>
-    <row r="26" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="16">
         <f t="shared" ca="1" si="0"/>
         <v>38</v>
@@ -12732,7 +12761,7 @@
       </c>
       <c r="O26" s="29"/>
     </row>
-    <row r="27" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="16">
         <f t="shared" ca="1" si="0"/>
         <v>39</v>
@@ -12764,7 +12793,7 @@
       <c r="N27" s="2"/>
       <c r="O27" s="29"/>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="16">
         <f t="shared" ca="1" si="0"/>
         <v>40</v>
@@ -12796,7 +12825,7 @@
       <c r="N28" s="2"/>
       <c r="O28" s="29"/>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="16">
         <f t="shared" ca="1" si="0"/>
         <v>41</v>
@@ -12828,7 +12857,7 @@
       <c r="N29" s="2"/>
       <c r="O29" s="29"/>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="16">
         <f t="shared" ca="1" si="0"/>
         <v>42</v>
@@ -12860,7 +12889,7 @@
       <c r="N30" s="2"/>
       <c r="O30" s="29"/>
     </row>
-    <row r="31" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A31" s="16">
         <f t="shared" ca="1" si="0"/>
         <v>43</v>
@@ -12894,7 +12923,7 @@
       </c>
       <c r="O31" s="29"/>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="16">
         <f t="shared" ca="1" si="0"/>
         <v>44</v>
@@ -12926,7 +12955,7 @@
       <c r="N32" s="2"/>
       <c r="O32" s="29"/>
     </row>
-    <row r="33" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="16">
         <f t="shared" ca="1" si="0"/>
         <v>45</v>
@@ -12958,7 +12987,7 @@
       <c r="N33" s="2"/>
       <c r="O33" s="29"/>
     </row>
-    <row r="34" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="16">
         <f t="shared" ca="1" si="0"/>
         <v>46</v>
@@ -12992,7 +13021,7 @@
       </c>
       <c r="O34" s="29"/>
     </row>
-    <row r="35" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A35" s="16">
         <f t="shared" ref="A35:A66" ca="1" si="1">A34+1</f>
         <v>47</v>
@@ -13020,7 +13049,7 @@
       <c r="N35" s="2"/>
       <c r="O35" s="29"/>
     </row>
-    <row r="36" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:15" ht="90" x14ac:dyDescent="0.25">
       <c r="A36" s="16">
         <f t="shared" ca="1" si="1"/>
         <v>48</v>
@@ -13054,7 +13083,7 @@
       <c r="N36" s="2"/>
       <c r="O36" s="29"/>
     </row>
-    <row r="37" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A37" s="16">
         <f t="shared" ca="1" si="1"/>
         <v>49</v>
@@ -13086,7 +13115,7 @@
       <c r="N37" s="2"/>
       <c r="O37" s="29"/>
     </row>
-    <row r="38" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="16">
         <f t="shared" ca="1" si="1"/>
         <v>50</v>
@@ -13118,7 +13147,7 @@
       <c r="N38" s="2"/>
       <c r="O38" s="29"/>
     </row>
-    <row r="39" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="16">
         <f t="shared" ca="1" si="1"/>
         <v>51</v>
@@ -13152,7 +13181,7 @@
       </c>
       <c r="O39" s="29"/>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="16">
         <f t="shared" ca="1" si="1"/>
         <v>52</v>
@@ -13184,7 +13213,7 @@
       <c r="N40" s="2"/>
       <c r="O40" s="29"/>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="16">
         <f t="shared" ca="1" si="1"/>
         <v>53</v>
@@ -13214,7 +13243,7 @@
       <c r="N41" s="2"/>
       <c r="O41" s="29"/>
     </row>
-    <row r="42" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A42" s="16">
         <f t="shared" ca="1" si="1"/>
         <v>54</v>
@@ -13246,7 +13275,7 @@
       <c r="N42" s="2"/>
       <c r="O42" s="29"/>
     </row>
-    <row r="43" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A43" s="16">
         <f t="shared" ca="1" si="1"/>
         <v>55</v>
@@ -13280,7 +13309,7 @@
       </c>
       <c r="O43" s="29"/>
     </row>
-    <row r="44" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A44" s="16">
         <f t="shared" ca="1" si="1"/>
         <v>56</v>
@@ -13312,7 +13341,7 @@
       <c r="N44" s="2"/>
       <c r="O44" s="29"/>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="16">
         <f t="shared" ca="1" si="1"/>
         <v>57</v>
@@ -13344,7 +13373,7 @@
       <c r="N45" s="2"/>
       <c r="O45" s="29"/>
     </row>
-    <row r="46" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="16">
         <f t="shared" ca="1" si="1"/>
         <v>58</v>
@@ -13378,7 +13407,7 @@
       </c>
       <c r="O46" s="29"/>
     </row>
-    <row r="47" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A47" s="16">
         <f t="shared" ca="1" si="1"/>
         <v>59</v>
@@ -13410,7 +13439,7 @@
       <c r="N47" s="2"/>
       <c r="O47" s="29"/>
     </row>
-    <row r="48" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A48" s="16">
         <f t="shared" ca="1" si="1"/>
         <v>60</v>
@@ -13442,7 +13471,7 @@
       <c r="N48" s="2"/>
       <c r="O48" s="29"/>
     </row>
-    <row r="49" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A49" s="16">
         <f t="shared" ca="1" si="1"/>
         <v>61</v>
@@ -13476,7 +13505,7 @@
       </c>
       <c r="O49" s="29"/>
     </row>
-    <row r="50" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A50" s="16">
         <f t="shared" ca="1" si="1"/>
         <v>62</v>
@@ -13508,7 +13537,7 @@
       <c r="N50" s="2"/>
       <c r="O50" s="29"/>
     </row>
-    <row r="51" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A51" s="16">
         <f t="shared" ca="1" si="1"/>
         <v>63</v>
@@ -13540,7 +13569,7 @@
       <c r="N51" s="2"/>
       <c r="O51" s="29"/>
     </row>
-    <row r="52" spans="1:15" ht="216" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:15" ht="240" x14ac:dyDescent="0.25">
       <c r="A52" s="16">
         <f t="shared" ca="1" si="1"/>
         <v>64</v>
@@ -13572,7 +13601,7 @@
       <c r="N52" s="2"/>
       <c r="O52" s="29"/>
     </row>
-    <row r="53" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A53" s="16">
         <f t="shared" ca="1" si="1"/>
         <v>65</v>
@@ -13606,7 +13635,7 @@
       </c>
       <c r="O53" s="29"/>
     </row>
-    <row r="54" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A54" s="16">
         <f t="shared" ca="1" si="1"/>
         <v>66</v>
@@ -13638,7 +13667,7 @@
       <c r="N54" s="2"/>
       <c r="O54" s="29"/>
     </row>
-    <row r="55" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A55" s="16">
         <f t="shared" ca="1" si="1"/>
         <v>67</v>
@@ -13670,7 +13699,7 @@
       <c r="N55" s="2"/>
       <c r="O55" s="29"/>
     </row>
-    <row r="56" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:15" ht="75" x14ac:dyDescent="0.25">
       <c r="A56" s="16">
         <f t="shared" ca="1" si="1"/>
         <v>68</v>
@@ -13704,7 +13733,7 @@
       </c>
       <c r="O56" s="29"/>
     </row>
-    <row r="57" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A57" s="16">
         <f t="shared" ca="1" si="1"/>
         <v>69</v>
@@ -13736,7 +13765,7 @@
       <c r="N57" s="2"/>
       <c r="O57" s="29"/>
     </row>
-    <row r="58" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A58" s="16">
         <f t="shared" ca="1" si="1"/>
         <v>70</v>
@@ -13768,7 +13797,7 @@
       <c r="N58" s="2"/>
       <c r="O58" s="29"/>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="16">
         <f t="shared" ca="1" si="1"/>
         <v>71</v>
@@ -13800,7 +13829,7 @@
       <c r="N59" s="2"/>
       <c r="O59" s="29"/>
     </row>
-    <row r="60" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:15" ht="90" x14ac:dyDescent="0.25">
       <c r="A60" s="16">
         <f t="shared" ca="1" si="1"/>
         <v>72</v>
@@ -13832,7 +13861,7 @@
       <c r="N60" s="2"/>
       <c r="O60" s="29"/>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="16">
         <f t="shared" ca="1" si="1"/>
         <v>73</v>
@@ -13864,7 +13893,7 @@
       <c r="N61" s="2"/>
       <c r="O61" s="29"/>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="16">
         <f t="shared" ca="1" si="1"/>
         <v>74</v>
@@ -13894,7 +13923,7 @@
       <c r="N62" s="2"/>
       <c r="O62" s="29"/>
     </row>
-    <row r="63" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A63" s="16">
         <f t="shared" ca="1" si="1"/>
         <v>75</v>
@@ -13926,7 +13955,7 @@
       <c r="N63" s="2"/>
       <c r="O63" s="29"/>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="16">
         <f t="shared" ca="1" si="1"/>
         <v>76</v>
@@ -13956,7 +13985,7 @@
       <c r="N64" s="2"/>
       <c r="O64" s="29"/>
     </row>
-    <row r="65" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A65" s="16">
         <f t="shared" ca="1" si="1"/>
         <v>77</v>
@@ -13986,7 +14015,7 @@
       <c r="N65" s="2"/>
       <c r="O65" s="29"/>
     </row>
-    <row r="66" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A66" s="16">
         <f t="shared" ca="1" si="1"/>
         <v>78</v>
@@ -14018,7 +14047,7 @@
       </c>
       <c r="O66" s="29"/>
     </row>
-    <row r="67" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:15" ht="90" x14ac:dyDescent="0.25">
       <c r="A67" s="16">
         <f t="shared" ref="A67:A92" ca="1" si="2">A66+1</f>
         <v>79</v>
@@ -14048,7 +14077,7 @@
       <c r="N67" s="2"/>
       <c r="O67" s="29"/>
     </row>
-    <row r="68" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:15" ht="75" x14ac:dyDescent="0.25">
       <c r="A68" s="16">
         <f t="shared" ca="1" si="2"/>
         <v>80</v>
@@ -14078,7 +14107,7 @@
       <c r="N68" s="2"/>
       <c r="O68" s="29"/>
     </row>
-    <row r="69" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A69" s="16">
         <f t="shared" ca="1" si="2"/>
         <v>81</v>
@@ -14108,7 +14137,7 @@
       <c r="N69" s="2"/>
       <c r="O69" s="29"/>
     </row>
-    <row r="70" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A70" s="16">
         <f t="shared" ca="1" si="2"/>
         <v>82</v>
@@ -14140,7 +14169,7 @@
       </c>
       <c r="O70" s="29"/>
     </row>
-    <row r="71" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:15" ht="75" x14ac:dyDescent="0.25">
       <c r="A71" s="16">
         <f t="shared" ca="1" si="2"/>
         <v>83</v>
@@ -14170,7 +14199,7 @@
       <c r="N71" s="2"/>
       <c r="O71" s="29"/>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="16">
         <f t="shared" ca="1" si="2"/>
         <v>84</v>
@@ -14200,7 +14229,7 @@
       <c r="N72" s="2"/>
       <c r="O72" s="29"/>
     </row>
-    <row r="73" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A73" s="16">
         <f t="shared" ca="1" si="2"/>
         <v>85</v>
@@ -14230,7 +14259,7 @@
       <c r="N73" s="2"/>
       <c r="O73" s="29"/>
     </row>
-    <row r="74" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A74" s="16">
         <f t="shared" ca="1" si="2"/>
         <v>86</v>
@@ -14260,7 +14289,7 @@
       <c r="N74" s="2"/>
       <c r="O74" s="29"/>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="16">
         <f t="shared" ca="1" si="2"/>
         <v>87</v>
@@ -14290,7 +14319,7 @@
       <c r="N75" s="2"/>
       <c r="O75" s="29"/>
     </row>
-    <row r="76" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A76" s="16">
         <f t="shared" ca="1" si="2"/>
         <v>88</v>
@@ -14322,7 +14351,7 @@
       </c>
       <c r="O76" s="29"/>
     </row>
-    <row r="77" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A77" s="16">
         <f t="shared" ca="1" si="2"/>
         <v>89</v>
@@ -14352,7 +14381,7 @@
       <c r="N77" s="2"/>
       <c r="O77" s="29"/>
     </row>
-    <row r="78" spans="1:15" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:15" ht="240" x14ac:dyDescent="0.25">
       <c r="A78" s="16">
         <f t="shared" ca="1" si="2"/>
         <v>90</v>
@@ -14382,7 +14411,7 @@
       <c r="N78" s="2"/>
       <c r="O78" s="29"/>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="16">
         <f t="shared" ca="1" si="2"/>
         <v>91</v>
@@ -14412,7 +14441,7 @@
       <c r="N79" s="2"/>
       <c r="O79" s="29"/>
     </row>
-    <row r="80" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:15" ht="75" x14ac:dyDescent="0.25">
       <c r="A80" s="16">
         <f t="shared" ca="1" si="2"/>
         <v>92</v>
@@ -14442,7 +14471,7 @@
       <c r="N80" s="2"/>
       <c r="O80" s="29"/>
     </row>
-    <row r="81" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A81" s="16">
         <f t="shared" ca="1" si="2"/>
         <v>93</v>
@@ -14472,7 +14501,7 @@
       <c r="N81" s="2"/>
       <c r="O81" s="29"/>
     </row>
-    <row r="82" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:17" ht="60" x14ac:dyDescent="0.25">
       <c r="A82" s="16">
         <f t="shared" ca="1" si="2"/>
         <v>94</v>
@@ -14504,7 +14533,7 @@
       <c r="N82" s="2"/>
       <c r="O82" s="29"/>
     </row>
-    <row r="83" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A83" s="16">
         <f t="shared" ca="1" si="2"/>
         <v>95</v>
@@ -14534,7 +14563,7 @@
       <c r="N83" s="2"/>
       <c r="O83" s="29"/>
     </row>
-    <row r="84" spans="1:17" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A84" s="16">
         <f t="shared" ca="1" si="2"/>
         <v>96</v>
@@ -14564,7 +14593,7 @@
       <c r="N84" s="2"/>
       <c r="O84" s="29"/>
     </row>
-    <row r="85" spans="1:17" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:17" ht="210" x14ac:dyDescent="0.25">
       <c r="A85" s="16">
         <f t="shared" ca="1" si="2"/>
         <v>97</v>
@@ -14596,7 +14625,7 @@
       <c r="N85" s="2"/>
       <c r="O85" s="29"/>
     </row>
-    <row r="86" spans="1:17" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:17" ht="60" x14ac:dyDescent="0.25">
       <c r="A86" s="16">
         <f t="shared" ca="1" si="2"/>
         <v>98</v>
@@ -14626,7 +14655,7 @@
       <c r="N86" s="2"/>
       <c r="O86" s="29"/>
     </row>
-    <row r="87" spans="1:17" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:17" ht="60" x14ac:dyDescent="0.25">
       <c r="A87" s="16">
         <f t="shared" ca="1" si="2"/>
         <v>99</v>
@@ -14656,7 +14685,7 @@
       <c r="N87" s="2"/>
       <c r="O87" s="29"/>
     </row>
-    <row r="88" spans="1:17" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:17" ht="120" x14ac:dyDescent="0.25">
       <c r="A88" s="16">
         <f t="shared" ca="1" si="2"/>
         <v>100</v>
@@ -14687,7 +14716,7 @@
       <c r="O88" s="2"/>
       <c r="P88" s="2"/>
     </row>
-    <row r="89" spans="1:17" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:17" ht="150" x14ac:dyDescent="0.25">
       <c r="A89" s="16">
         <f t="shared" ca="1" si="2"/>
         <v>101</v>
@@ -14718,7 +14747,7 @@
       <c r="O89" s="2"/>
       <c r="P89" s="2"/>
     </row>
-    <row r="90" spans="1:17" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A90" s="16">
         <f t="shared" ca="1" si="2"/>
         <v>102</v>
@@ -14749,7 +14778,7 @@
       <c r="O90" s="2"/>
       <c r="P90" s="2"/>
     </row>
-    <row r="91" spans="1:17" ht="75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:17" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="16">
         <f t="shared" ca="1" si="2"/>
         <v>103</v>
@@ -14783,7 +14812,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="92" spans="1:17" ht="150" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:17" ht="150" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="16">
         <f t="shared" ca="1" si="2"/>
         <v>104</v>
@@ -14826,187 +14855,175 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66B5E853-2798-4156-AAAB-0750264D3328}">
-  <dimension ref="A1:P27"/>
-  <sheetFormatPr defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:R28"/>
+  <sheetFormatPr defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="36.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="30.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.109375" customWidth="1"/>
-    <col min="8" max="8" width="65.88671875" customWidth="1"/>
-    <col min="13" max="13" width="26.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.140625" customWidth="1"/>
+    <col min="8" max="8" width="65.85546875" customWidth="1"/>
+    <col min="13" max="13" width="26.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="75" t="s">
+    <row r="1" spans="1:18" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="77" t="s">
         <v>280</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-      <c r="H1" s="75"/>
-      <c r="I1" s="75"/>
-      <c r="J1" s="75"/>
-      <c r="K1" s="75"/>
-      <c r="L1" s="75"/>
-      <c r="M1" s="75"/>
-      <c r="N1" s="75"/>
-    </row>
-    <row r="2" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="76" t="s">
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
+      <c r="L1" s="77"/>
+      <c r="M1" s="77"/>
+      <c r="N1" s="77"/>
+    </row>
+    <row r="2" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+      <c r="A2" s="93" t="s">
+        <v>784</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>785</v>
+      </c>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="94"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="R2" s="20"/>
+    </row>
+    <row r="3" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="66" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="76"/>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
-      <c r="K2" s="76"/>
-      <c r="L2" s="76"/>
-      <c r="M2" s="76"/>
-      <c r="N2" s="76"/>
-    </row>
-    <row r="3" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="78" t="s">
+      <c r="B3" s="66"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="66"/>
+      <c r="K3" s="66"/>
+      <c r="L3" s="66"/>
+      <c r="M3" s="66"/>
+      <c r="N3" s="66"/>
+    </row>
+    <row r="4" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="67" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="78"/>
-      <c r="C3" s="78"/>
-      <c r="D3" s="78"/>
-      <c r="E3" s="78"/>
-      <c r="F3" s="78"/>
-      <c r="G3" s="78"/>
-      <c r="H3" s="78"/>
-      <c r="I3" s="78"/>
-      <c r="J3" s="78"/>
-      <c r="K3" s="78"/>
-      <c r="L3" s="78"/>
-      <c r="M3" s="78"/>
-      <c r="N3" s="78"/>
-    </row>
-    <row r="4" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="76" t="s">
+      <c r="B4" s="67"/>
+      <c r="C4" s="67"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="67"/>
+      <c r="J4" s="67"/>
+      <c r="K4" s="67"/>
+      <c r="L4" s="67"/>
+      <c r="M4" s="67"/>
+      <c r="N4" s="67"/>
+    </row>
+    <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="66" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="76"/>
-      <c r="C4" s="76"/>
-      <c r="D4" s="76"/>
-      <c r="E4" s="76"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="76"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="76"/>
-      <c r="K4" s="76"/>
-      <c r="L4" s="76"/>
-      <c r="M4" s="76"/>
-      <c r="N4" s="76"/>
-    </row>
-    <row r="5" spans="1:16" ht="41.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
+      <c r="B5" s="66"/>
+      <c r="C5" s="66"/>
+      <c r="D5" s="66"/>
+      <c r="E5" s="66"/>
+      <c r="F5" s="66"/>
+      <c r="G5" s="66"/>
+      <c r="H5" s="66"/>
+      <c r="I5" s="66"/>
+      <c r="J5" s="66"/>
+      <c r="K5" s="66"/>
+      <c r="L5" s="66"/>
+      <c r="M5" s="66"/>
+      <c r="N5" s="66"/>
+    </row>
+    <row r="6" spans="1:18" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B6" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C6" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D6" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E6" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F6" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G6" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H6" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="I5" s="9" t="s">
+      <c r="I6" s="9" t="s">
         <v>281</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="J6" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="K5" s="5" t="s">
+      <c r="K6" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="L5" s="5" t="s">
+      <c r="L6" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="M5" s="5" t="s">
+      <c r="M6" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="N5" s="6" t="s">
+      <c r="N6" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="O5" s="9" t="s">
+      <c r="O6" s="9" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
+    <row r="7" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
         <v>1</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="44" t="s">
-        <v>60</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="I6" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
-      <c r="O6" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="16" cm="1">
-        <f t="array" aca="1" ref="A7" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>2</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="44" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>64</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="I7" s="41" t="s">
         <v>62</v>
@@ -15022,31 +15039,33 @@
         <v>62</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16" cm="1">
         <f t="array" aca="1" ref="A8" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="44" t="s">
-        <v>96</v>
+        <v>65</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="I8" s="41" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
+      <c r="K8" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
@@ -15054,66 +15073,65 @@
         <v>62</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="16" cm="1">
         <f t="array" aca="1" ref="A9" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="44" t="s">
-        <v>67</v>
+        <v>96</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>61</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>68</v>
+        <v>284</v>
       </c>
       <c r="I9" s="41" t="s">
         <v>64</v>
       </c>
       <c r="J9" s="2"/>
-      <c r="K9" s="2" t="s">
-        <v>64</v>
-      </c>
+      <c r="K9" s="2"/>
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
       <c r="O9" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="P9" s="35"/>
-    </row>
-    <row r="10" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="16" cm="1">
         <f t="array" aca="1" ref="A10" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
       <c r="E10" s="44" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>64</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I10" s="41" t="s">
         <v>64</v>
       </c>
       <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
+      <c r="K10" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
@@ -15122,28 +15140,28 @@
       </c>
       <c r="P10" s="35"/>
     </row>
-    <row r="11" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" ht="15" x14ac:dyDescent="0.25">
       <c r="A11" s="16" cm="1">
         <f t="array" aca="1" ref="A11" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
       <c r="E11" s="44" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>64</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I11" s="41" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
@@ -15155,16 +15173,16 @@
       </c>
       <c r="P11" s="35"/>
     </row>
-    <row r="12" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="16" cm="1">
         <f t="array" aca="1" ref="A12" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="44" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>61</v>
@@ -15173,35 +15191,31 @@
         <v>64</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>285</v>
+        <v>73</v>
       </c>
       <c r="I12" s="41" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="J12" s="2"/>
-      <c r="K12" s="2" t="s">
-        <v>64</v>
-      </c>
+      <c r="K12" s="2"/>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
       <c r="O12" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="P12" s="35" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="P12" s="35"/>
+    </row>
+    <row r="13" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="16" cm="1">
         <f t="array" aca="1" ref="A13" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="44" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>61</v>
@@ -15210,7 +15224,7 @@
         <v>64</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="I13" s="41" t="s">
         <v>64</v>
@@ -15229,57 +15243,61 @@
         <v>62</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="16" cm="1">
         <f t="array" aca="1" ref="A14" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
       <c r="E14" s="44" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="H14" s="3"/>
+      <c r="H14" s="3" t="s">
+        <v>286</v>
+      </c>
       <c r="I14" s="41" t="s">
         <v>64</v>
       </c>
       <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
+      <c r="K14" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
       <c r="O14" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="P14" s="35"/>
-    </row>
-    <row r="15" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P14" s="35" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="16" cm="1">
         <f t="array" aca="1" ref="A15" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
       <c r="E15" s="44" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>80</v>
-      </c>
+      <c r="H15" s="3"/>
       <c r="I15" s="41" t="s">
         <v>64</v>
       </c>
@@ -15293,53 +15311,49 @@
       </c>
       <c r="P15" s="35"/>
     </row>
-    <row r="16" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="16" cm="1">
         <f t="array" aca="1" ref="A16" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
       <c r="E16" s="44" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>64</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>287</v>
+        <v>80</v>
       </c>
       <c r="I16" s="41" t="s">
         <v>64</v>
       </c>
-      <c r="J16" s="3" t="s">
-        <v>83</v>
-      </c>
+      <c r="J16" s="2"/>
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
       <c r="M16" s="2"/>
-      <c r="N16" s="2" t="s">
-        <v>84</v>
-      </c>
+      <c r="N16" s="2"/>
       <c r="O16" s="2" t="s">
         <v>64</v>
       </c>
       <c r="P16" s="35"/>
     </row>
-    <row r="17" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="16" cm="1">
         <f t="array" aca="1" ref="A17" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
       <c r="E17" s="44" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>61</v>
@@ -15348,7 +15362,7 @@
         <v>64</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I17" s="41" t="s">
         <v>64</v>
@@ -15359,42 +15373,42 @@
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
       <c r="M17" s="2"/>
-      <c r="N17" s="2"/>
+      <c r="N17" s="2" t="s">
+        <v>84</v>
+      </c>
       <c r="O17" s="2" t="s">
         <v>64</v>
       </c>
       <c r="P17" s="35"/>
     </row>
-    <row r="18" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="16" cm="1">
         <f t="array" aca="1" ref="A18" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
       <c r="E18" s="44" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="H18" s="3"/>
+      <c r="H18" s="3" t="s">
+        <v>288</v>
+      </c>
       <c r="I18" s="41" t="s">
         <v>64</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>64</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
       <c r="M18" s="2"/>
       <c r="N18" s="2"/>
       <c r="O18" s="2" t="s">
@@ -15402,19 +15416,19 @@
       </c>
       <c r="P18" s="35"/>
     </row>
-    <row r="19" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="16" cm="1">
         <f t="array" aca="1" ref="A19" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
       <c r="E19" s="44" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>64</v>
@@ -15423,7 +15437,9 @@
       <c r="I19" s="41" t="s">
         <v>64</v>
       </c>
-      <c r="J19" s="3"/>
+      <c r="J19" s="3" t="s">
+        <v>88</v>
+      </c>
       <c r="K19" s="2" t="s">
         <v>64</v>
       </c>
@@ -15437,154 +15453,154 @@
       </c>
       <c r="P19" s="35"/>
     </row>
-    <row r="20" spans="1:16" s="4" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="16" cm="1">
         <f t="array" aca="1" ref="A20" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
+        <v>14</v>
+      </c>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="44" t="s">
+        <v>89</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H20" s="3"/>
+      <c r="I20" s="41" t="s">
+        <v>64</v>
+      </c>
+      <c r="J20" s="3"/>
+      <c r="K20" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="P20" s="35"/>
+    </row>
+    <row r="21" spans="1:16" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A21" s="16" cm="1">
+        <f t="array" aca="1" ref="A21" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>15</v>
       </c>
-      <c r="B20" s="45"/>
-      <c r="C20" s="45"/>
-      <c r="D20" s="45"/>
-      <c r="E20" s="46" t="s">
+      <c r="B21" s="45"/>
+      <c r="C21" s="45"/>
+      <c r="D21" s="45"/>
+      <c r="E21" s="46" t="s">
         <v>98</v>
       </c>
-      <c r="F20" s="45" t="s">
+      <c r="F21" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="G20" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="H20" s="56" t="s">
+      <c r="G21" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="H21" s="56" t="s">
         <v>289</v>
       </c>
-      <c r="I20" s="41" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="72" t="s">
+      <c r="I21" s="41" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="68" t="s">
         <v>90</v>
       </c>
-      <c r="B21" s="82"/>
-      <c r="C21" s="82"/>
-      <c r="D21" s="82"/>
-      <c r="E21" s="82"/>
-      <c r="F21" s="82"/>
-      <c r="G21" s="82"/>
-      <c r="H21" s="82"/>
-      <c r="I21" s="82"/>
-      <c r="J21" s="82"/>
-      <c r="K21" s="82"/>
-      <c r="L21" s="82"/>
-      <c r="M21" s="82"/>
-      <c r="N21" s="83"/>
-    </row>
-    <row r="22" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="11" t="s">
+      <c r="B22" s="69"/>
+      <c r="C22" s="69"/>
+      <c r="D22" s="69"/>
+      <c r="E22" s="69"/>
+      <c r="F22" s="69"/>
+      <c r="G22" s="69"/>
+      <c r="H22" s="69"/>
+      <c r="I22" s="69"/>
+      <c r="J22" s="69"/>
+      <c r="K22" s="69"/>
+      <c r="L22" s="69"/>
+      <c r="M22" s="69"/>
+      <c r="N22" s="70"/>
+    </row>
+    <row r="23" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B23" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C23" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D23" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="E23" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="F23" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="G22" s="5" t="s">
+      <c r="G23" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="H22" s="5" t="s">
+      <c r="H23" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="I22" s="5" t="s">
+      <c r="I23" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="J22" s="5" t="s">
+      <c r="J23" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="K22" s="5" t="s">
+      <c r="K23" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="L22" s="6" t="s">
+      <c r="L23" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="M22" s="9" t="s">
+      <c r="M23" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="N22" s="9" t="s">
+      <c r="N23" s="9" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="17">
+    <row r="24" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="17">
         <v>1</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C23" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="D23" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G23" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="I23" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="J23" s="2"/>
-      <c r="K23" s="2"/>
-      <c r="L23" s="2"/>
-      <c r="M23" s="2"/>
-      <c r="N23" s="2"/>
-    </row>
-    <row r="24" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="16" cm="1">
-        <f t="array" aca="1" ref="A24" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>2</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>91</v>
       </c>
       <c r="C24" s="22" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D24" s="22" t="s">
         <v>62</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="G24" s="12" t="s">
         <v>62</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I24" s="12" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
@@ -15592,22 +15608,22 @@
       <c r="M24" s="2"/>
       <c r="N24" s="2"/>
     </row>
-    <row r="25" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="16" cm="1">
         <f t="array" aca="1" ref="A25" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>91</v>
       </c>
       <c r="C25" s="22" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D25" s="22" t="s">
         <v>62</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>61</v>
@@ -15616,23 +15632,21 @@
         <v>62</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>64</v>
+        <v>95</v>
+      </c>
+      <c r="I25" s="12" t="s">
+        <v>62</v>
       </c>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
       <c r="M25" s="2"/>
-      <c r="N25" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N25" s="2"/>
+    </row>
+    <row r="26" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="16" cm="1">
         <f t="array" aca="1" ref="A26" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>91</v>
@@ -15644,16 +15658,16 @@
         <v>62</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>99</v>
+        <v>61</v>
       </c>
       <c r="G26" s="12" t="s">
         <v>62</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>64</v>
@@ -15666,22 +15680,59 @@
         <v>64</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="14" t="s">
+    <row r="27" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="16" cm="1">
+        <f t="array" aca="1" ref="A27" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
+        <v>4</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C27" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="D27" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G27" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="2"/>
+      <c r="M27" s="2"/>
+      <c r="N27" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="14" t="s">
         <v>101</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="I1:I27" xr:uid="{66B5E853-2798-4156-AAAB-0750264D3328}"/>
+  <autoFilter ref="I1:I28" xr:uid="{66B5E853-2798-4156-AAAB-0750264D3328}"/>
   <mergeCells count="5">
     <mergeCell ref="A1:N1"/>
-    <mergeCell ref="A2:N2"/>
     <mergeCell ref="A3:N3"/>
     <mergeCell ref="A4:N4"/>
-    <mergeCell ref="A21:N21"/>
+    <mergeCell ref="A5:N5"/>
+    <mergeCell ref="A22:N22"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A27" location="Index!A1" display="Back to Index" xr:uid="{CCAE1ABC-0F17-4336-B0AA-0AE835154C43}"/>
+    <hyperlink ref="A28" location="Index!A1" display="Back to Index" xr:uid="{CCAE1ABC-0F17-4336-B0AA-0AE835154C43}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -15691,105 +15742,105 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5684969F-AACD-45AF-A496-A79457D4E01D}">
   <dimension ref="A1:N13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="36.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31.109375" customWidth="1"/>
-    <col min="6" max="6" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="51.33203125" customWidth="1"/>
+    <col min="2" max="2" width="36.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.140625" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="51.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="75" t="s">
+    <row r="1" spans="1:14" s="4" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="77" t="s">
         <v>290</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-      <c r="H1" s="75"/>
-      <c r="I1" s="75"/>
-      <c r="J1" s="75"/>
-      <c r="K1" s="75"/>
-      <c r="L1" s="75"/>
-      <c r="M1" s="75"/>
-      <c r="N1" s="75"/>
-    </row>
-    <row r="2" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A2" s="76" t="s">
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
+      <c r="L1" s="77"/>
+      <c r="M1" s="77"/>
+      <c r="N1" s="77"/>
+    </row>
+    <row r="2" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A2" s="66" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="76"/>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
-      <c r="K2" s="76"/>
-      <c r="L2" s="76"/>
-      <c r="M2" s="76"/>
-      <c r="N2" s="76"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3" s="78" t="s">
+      <c r="B2" s="66"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="66"/>
+      <c r="I2" s="66"/>
+      <c r="J2" s="66"/>
+      <c r="K2" s="66"/>
+      <c r="L2" s="66"/>
+      <c r="M2" s="66"/>
+      <c r="N2" s="66"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="67" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="78"/>
-      <c r="C3" s="78"/>
-      <c r="D3" s="78"/>
-      <c r="E3" s="78"/>
-      <c r="F3" s="78"/>
-      <c r="G3" s="78"/>
-      <c r="H3" s="78"/>
-      <c r="I3" s="78"/>
-      <c r="J3" s="78"/>
-      <c r="K3" s="78"/>
-      <c r="L3" s="78"/>
-      <c r="M3" s="78"/>
-      <c r="N3" s="78"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="84" t="s">
+      <c r="B3" s="67"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="67"/>
+      <c r="G3" s="67"/>
+      <c r="H3" s="67"/>
+      <c r="I3" s="67"/>
+      <c r="J3" s="67"/>
+      <c r="K3" s="67"/>
+      <c r="L3" s="67"/>
+      <c r="M3" s="67"/>
+      <c r="N3" s="67"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="82" t="s">
         <v>291</v>
       </c>
-      <c r="B4" s="84"/>
-      <c r="C4" s="84"/>
-      <c r="D4" s="84"/>
-      <c r="E4" s="84"/>
-      <c r="F4" s="84"/>
-      <c r="G4" s="84"/>
-      <c r="H4" s="84"/>
-      <c r="I4" s="84"/>
-      <c r="J4" s="84"/>
-      <c r="K4" s="84"/>
-      <c r="L4" s="84"/>
-      <c r="M4" s="84"/>
-      <c r="N4" s="84"/>
-    </row>
-    <row r="5" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A5" s="76" t="s">
+      <c r="B4" s="82"/>
+      <c r="C4" s="82"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="82"/>
+      <c r="F4" s="82"/>
+      <c r="G4" s="82"/>
+      <c r="H4" s="82"/>
+      <c r="I4" s="82"/>
+      <c r="J4" s="82"/>
+      <c r="K4" s="82"/>
+      <c r="L4" s="82"/>
+      <c r="M4" s="82"/>
+      <c r="N4" s="82"/>
+    </row>
+    <row r="5" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A5" s="66" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="76"/>
-      <c r="C5" s="76"/>
-      <c r="D5" s="76"/>
-      <c r="E5" s="76"/>
-      <c r="F5" s="76"/>
-      <c r="G5" s="76"/>
-      <c r="H5" s="76"/>
-      <c r="I5" s="76"/>
-      <c r="J5" s="76"/>
-      <c r="K5" s="76"/>
-      <c r="L5" s="76"/>
-      <c r="M5" s="76"/>
-      <c r="N5" s="76"/>
-    </row>
-    <row r="6" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="B5" s="66"/>
+      <c r="C5" s="66"/>
+      <c r="D5" s="66"/>
+      <c r="E5" s="66"/>
+      <c r="F5" s="66"/>
+      <c r="G5" s="66"/>
+      <c r="H5" s="66"/>
+      <c r="I5" s="66"/>
+      <c r="J5" s="66"/>
+      <c r="K5" s="66"/>
+      <c r="L5" s="66"/>
+      <c r="M5" s="66"/>
+      <c r="N5" s="66"/>
+    </row>
+    <row r="6" spans="1:14" ht="120" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>43</v>
       </c>
@@ -15833,7 +15884,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>1</v>
       </c>
@@ -15863,25 +15914,25 @@
         <v>62</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A8" s="72" t="s">
+    <row r="8" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A8" s="68" t="s">
         <v>90</v>
       </c>
-      <c r="B8" s="82"/>
-      <c r="C8" s="82"/>
-      <c r="D8" s="82"/>
-      <c r="E8" s="82"/>
-      <c r="F8" s="82"/>
-      <c r="G8" s="82"/>
-      <c r="H8" s="82"/>
-      <c r="I8" s="82"/>
-      <c r="J8" s="82"/>
-      <c r="K8" s="82"/>
-      <c r="L8" s="82"/>
-      <c r="M8" s="82"/>
-      <c r="N8" s="83"/>
-    </row>
-    <row r="9" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="B8" s="69"/>
+      <c r="C8" s="69"/>
+      <c r="D8" s="69"/>
+      <c r="E8" s="69"/>
+      <c r="F8" s="69"/>
+      <c r="G8" s="69"/>
+      <c r="H8" s="69"/>
+      <c r="I8" s="69"/>
+      <c r="J8" s="69"/>
+      <c r="K8" s="69"/>
+      <c r="L8" s="69"/>
+      <c r="M8" s="69"/>
+      <c r="N8" s="70"/>
+    </row>
+    <row r="9" spans="1:14" ht="120" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>43</v>
       </c>
@@ -15925,7 +15976,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="17">
         <v>1</v>
       </c>
@@ -15959,7 +16010,7 @@
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="17">
         <f>A10+1</f>
         <v>2</v>
@@ -15992,7 +16043,7 @@
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="17">
         <f>A11+1</f>
         <v>3</v>
@@ -16025,7 +16076,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
         <v>101</v>
       </c>
@@ -16048,358 +16099,347 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6B4A248-C735-4C63-971A-A3F0609388EA}">
-  <dimension ref="A1:N16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:R17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" style="4" customWidth="1"/>
-    <col min="2" max="2" width="36.109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="9.109375" style="8"/>
-    <col min="5" max="5" width="28.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.33203125" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" customWidth="1"/>
-    <col min="8" max="8" width="55.33203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="5.28515625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="36.140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="9.140625" style="8"/>
+    <col min="5" max="5" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" customWidth="1"/>
+    <col min="7" max="7" width="13.28515625" customWidth="1"/>
+    <col min="8" max="8" width="55.28515625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="4" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="85" t="s">
+    <row r="1" spans="1:18" s="4" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="83" t="s">
         <v>293</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
-      <c r="D1" s="85"/>
-      <c r="E1" s="85"/>
-      <c r="F1" s="85"/>
-      <c r="G1" s="85"/>
-      <c r="H1" s="85"/>
-      <c r="I1" s="85"/>
-      <c r="J1" s="85"/>
-      <c r="K1" s="85"/>
-      <c r="L1" s="85"/>
-      <c r="M1" s="85"/>
-      <c r="N1" s="85"/>
-    </row>
-    <row r="2" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A2" s="76" t="s">
+      <c r="B1" s="83"/>
+      <c r="C1" s="83"/>
+      <c r="D1" s="83"/>
+      <c r="E1" s="83"/>
+      <c r="F1" s="83"/>
+      <c r="G1" s="83"/>
+      <c r="H1" s="83"/>
+      <c r="I1" s="83"/>
+      <c r="J1" s="83"/>
+      <c r="K1" s="83"/>
+      <c r="L1" s="83"/>
+      <c r="M1" s="83"/>
+      <c r="N1" s="83"/>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="93" t="s">
+        <v>784</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>785</v>
+      </c>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="94"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="R2" s="20"/>
+    </row>
+    <row r="3" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A3" s="66" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="76"/>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
-      <c r="K2" s="76"/>
-      <c r="L2" s="76"/>
-      <c r="M2" s="76"/>
-      <c r="N2" s="76"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3" s="78" t="s">
+      <c r="B3" s="66"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="66"/>
+      <c r="K3" s="66"/>
+      <c r="L3" s="66"/>
+      <c r="M3" s="66"/>
+      <c r="N3" s="66"/>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" s="67" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="78"/>
-      <c r="C3" s="78"/>
-      <c r="D3" s="78"/>
-      <c r="E3" s="78"/>
-      <c r="F3" s="78"/>
-      <c r="G3" s="78"/>
-      <c r="H3" s="78"/>
-      <c r="I3" s="78"/>
-      <c r="J3" s="78"/>
-      <c r="K3" s="78"/>
-      <c r="L3" s="78"/>
-      <c r="M3" s="78"/>
-      <c r="N3" s="78"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="78" t="s">
+      <c r="B4" s="67"/>
+      <c r="C4" s="67"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="67"/>
+      <c r="J4" s="67"/>
+      <c r="K4" s="67"/>
+      <c r="L4" s="67"/>
+      <c r="M4" s="67"/>
+      <c r="N4" s="67"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A5" s="67" t="s">
         <v>294</v>
       </c>
-      <c r="B4" s="78"/>
-      <c r="C4" s="78"/>
-      <c r="D4" s="78"/>
-      <c r="E4" s="78"/>
-      <c r="F4" s="78"/>
-      <c r="G4" s="78"/>
-      <c r="H4" s="78"/>
-      <c r="I4" s="78"/>
-      <c r="J4" s="78"/>
-      <c r="K4" s="78"/>
-      <c r="L4" s="78"/>
-      <c r="M4" s="78"/>
-      <c r="N4" s="78"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A5" s="78" t="s">
+      <c r="B5" s="67"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="67"/>
+      <c r="K5" s="67"/>
+      <c r="L5" s="67"/>
+      <c r="M5" s="67"/>
+      <c r="N5" s="67"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" s="67" t="s">
         <v>295</v>
       </c>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
-      <c r="K5" s="78"/>
-      <c r="L5" s="78"/>
-      <c r="M5" s="78"/>
-      <c r="N5" s="78"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A6" s="78" t="s">
+      <c r="B6" s="67"/>
+      <c r="C6" s="67"/>
+      <c r="D6" s="67"/>
+      <c r="E6" s="67"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="67"/>
+      <c r="H6" s="67"/>
+      <c r="I6" s="67"/>
+      <c r="J6" s="67"/>
+      <c r="K6" s="67"/>
+      <c r="L6" s="67"/>
+      <c r="M6" s="67"/>
+      <c r="N6" s="67"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" s="67" t="s">
         <v>296</v>
       </c>
-      <c r="B6" s="78"/>
-      <c r="C6" s="78"/>
-      <c r="D6" s="78"/>
-      <c r="E6" s="78"/>
-      <c r="F6" s="78"/>
-      <c r="G6" s="78"/>
-      <c r="H6" s="78"/>
-      <c r="I6" s="78"/>
-      <c r="J6" s="78"/>
-      <c r="K6" s="78"/>
-      <c r="L6" s="78"/>
-      <c r="M6" s="78"/>
-      <c r="N6" s="78"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="78" t="s">
+      <c r="B7" s="67"/>
+      <c r="C7" s="67"/>
+      <c r="D7" s="67"/>
+      <c r="E7" s="67"/>
+      <c r="F7" s="67"/>
+      <c r="G7" s="67"/>
+      <c r="H7" s="67"/>
+      <c r="I7" s="67"/>
+      <c r="J7" s="67"/>
+      <c r="K7" s="67"/>
+      <c r="L7" s="67"/>
+      <c r="M7" s="67"/>
+      <c r="N7" s="67"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A8" s="67" t="s">
         <v>40</v>
       </c>
-      <c r="B7" s="78"/>
-      <c r="C7" s="78"/>
-      <c r="D7" s="78"/>
-      <c r="E7" s="78"/>
-      <c r="F7" s="78"/>
-      <c r="G7" s="78"/>
-      <c r="H7" s="78"/>
-      <c r="I7" s="78"/>
-      <c r="J7" s="78"/>
-      <c r="K7" s="78"/>
-      <c r="L7" s="78"/>
-      <c r="M7" s="78"/>
-      <c r="N7" s="78"/>
-    </row>
-    <row r="8" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A8" s="76" t="s">
+      <c r="B8" s="67"/>
+      <c r="C8" s="67"/>
+      <c r="D8" s="67"/>
+      <c r="E8" s="67"/>
+      <c r="F8" s="67"/>
+      <c r="G8" s="67"/>
+      <c r="H8" s="67"/>
+      <c r="I8" s="67"/>
+      <c r="J8" s="67"/>
+      <c r="K8" s="67"/>
+      <c r="L8" s="67"/>
+      <c r="M8" s="67"/>
+      <c r="N8" s="67"/>
+    </row>
+    <row r="9" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A9" s="66" t="s">
         <v>41</v>
       </c>
-      <c r="B8" s="76"/>
-      <c r="C8" s="76"/>
-      <c r="D8" s="76"/>
-      <c r="E8" s="76"/>
-      <c r="F8" s="76"/>
-      <c r="G8" s="76"/>
-      <c r="H8" s="76"/>
-      <c r="I8" s="76"/>
-      <c r="J8" s="76"/>
-      <c r="K8" s="76"/>
-      <c r="L8" s="76"/>
-      <c r="M8" s="76"/>
-      <c r="N8" s="76"/>
-    </row>
-    <row r="9" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
+      <c r="B9" s="66"/>
+      <c r="C9" s="66"/>
+      <c r="D9" s="66"/>
+      <c r="E9" s="66"/>
+      <c r="F9" s="66"/>
+      <c r="G9" s="66"/>
+      <c r="H9" s="66"/>
+      <c r="I9" s="66"/>
+      <c r="J9" s="66"/>
+      <c r="K9" s="66"/>
+      <c r="L9" s="66"/>
+      <c r="M9" s="66"/>
+      <c r="N9" s="66"/>
+    </row>
+    <row r="10" spans="1:18" ht="120" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B10" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C10" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D10" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E10" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F10" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="G10" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="H10" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="I9" s="5" t="s">
+      <c r="I10" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="J9" s="5" t="s">
+      <c r="J10" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="K9" s="5" t="s">
+      <c r="K10" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="L9" s="6" t="s">
+      <c r="L10" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="M9" s="9" t="s">
+      <c r="M10" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="N9" s="9" t="s">
+      <c r="N10" s="9" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="2">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
         <v>1</v>
       </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2" t="s">
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F11" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="G10" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="H10" s="2" t="s">
+      <c r="G11" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="I10" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-      <c r="N10" s="12" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A11" s="76" t="s">
+      <c r="I11" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="12" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A12" s="66" t="s">
         <v>298</v>
       </c>
-      <c r="B11" s="76"/>
-      <c r="C11" s="76"/>
-      <c r="D11" s="76"/>
-      <c r="E11" s="76"/>
-      <c r="F11" s="76"/>
-      <c r="G11" s="76"/>
-      <c r="H11" s="76"/>
-      <c r="I11" s="76"/>
-      <c r="J11" s="76"/>
-      <c r="K11" s="76"/>
-      <c r="L11" s="76"/>
-      <c r="M11" s="76"/>
-      <c r="N11" s="76"/>
-    </row>
-    <row r="12" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="11" t="s">
+      <c r="B12" s="66"/>
+      <c r="C12" s="66"/>
+      <c r="D12" s="66"/>
+      <c r="E12" s="66"/>
+      <c r="F12" s="66"/>
+      <c r="G12" s="66"/>
+      <c r="H12" s="66"/>
+      <c r="I12" s="66"/>
+      <c r="J12" s="66"/>
+      <c r="K12" s="66"/>
+      <c r="L12" s="66"/>
+      <c r="M12" s="66"/>
+      <c r="N12" s="66"/>
+    </row>
+    <row r="13" spans="1:18" ht="120" x14ac:dyDescent="0.25">
+      <c r="A13" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B13" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C13" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D13" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E13" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F13" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="G13" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="H12" s="5" t="s">
+      <c r="H13" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="I12" s="5" t="s">
+      <c r="I13" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="J12" s="5" t="s">
+      <c r="J13" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="K12" s="5" t="s">
+      <c r="K13" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="L12" s="6" t="s">
+      <c r="L13" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="M12" s="9" t="s">
+      <c r="M13" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="N12" s="9" t="s">
+      <c r="N13" s="9" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="17">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A14" s="17">
         <v>1</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C13" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="D13" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G13" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="I13" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="17">
-        <f>A13+1</f>
-        <v>2</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>91</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="D14" s="22"/>
+        <v>64</v>
+      </c>
+      <c r="D14" s="22" t="s">
+        <v>62</v>
+      </c>
       <c r="E14" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="G14" s="12" t="s">
         <v>62</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
@@ -16407,58 +16447,91 @@
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="17">
         <f>A14+1</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>91</v>
       </c>
       <c r="C15" s="22" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D15" s="22"/>
       <c r="E15" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>99</v>
+        <v>61</v>
       </c>
       <c r="G15" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="I15" s="2"/>
+      <c r="H15" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="I15" s="12" t="s">
+        <v>62</v>
+      </c>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
-      <c r="N15" s="22" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="14" t="s">
+      <c r="N15" s="2"/>
+    </row>
+    <row r="16" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="17">
+        <f>A15+1</f>
+        <v>3</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="D16" s="22"/>
+      <c r="E16" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="22" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="14" t="s">
         <v>101</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A6:N6"/>
     <mergeCell ref="A7:N7"/>
     <mergeCell ref="A8:N8"/>
-    <mergeCell ref="A11:N11"/>
+    <mergeCell ref="A9:N9"/>
+    <mergeCell ref="A12:N12"/>
     <mergeCell ref="A1:N1"/>
-    <mergeCell ref="A2:N2"/>
     <mergeCell ref="A3:N3"/>
     <mergeCell ref="A4:N4"/>
     <mergeCell ref="A5:N5"/>
+    <mergeCell ref="A6:N6"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A16" location="Index!A1" display="Back to Index" xr:uid="{2F7D9EE4-2416-40C7-AB98-A784D7AA5B56}"/>
+    <hyperlink ref="A17" location="Index!A1" display="Back to Index" xr:uid="{2F7D9EE4-2416-40C7-AB98-A784D7AA5B56}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -16468,54 +16541,54 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4851DCD-305D-4BC9-A3EE-700C77EE9B14}">
   <dimension ref="A1:O40"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
-    <col min="2" max="2" width="26.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="13.44140625" customWidth="1"/>
-    <col min="5" max="5" width="39.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="13.42578125" customWidth="1"/>
+    <col min="5" max="5" width="39.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20" customWidth="1"/>
-    <col min="8" max="8" width="14.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="33.5546875" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="33.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="76" t="s">
+    <row r="1" spans="1:15" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="66" t="s">
         <v>300</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
-      <c r="H1" s="76"/>
-      <c r="I1" s="76"/>
-      <c r="J1" s="76"/>
-      <c r="K1" s="76"/>
-      <c r="L1" s="76"/>
-      <c r="M1" s="76"/>
-      <c r="N1" s="76"/>
-    </row>
-    <row r="2" spans="1:15" ht="18" x14ac:dyDescent="0.35">
-      <c r="A2" s="76" t="s">
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="66"/>
+      <c r="H1" s="66"/>
+      <c r="I1" s="66"/>
+      <c r="J1" s="66"/>
+      <c r="K1" s="66"/>
+      <c r="L1" s="66"/>
+      <c r="M1" s="66"/>
+      <c r="N1" s="66"/>
+    </row>
+    <row r="2" spans="1:15" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A2" s="66" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="76"/>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
-      <c r="K2" s="76"/>
-      <c r="L2" s="76"/>
-      <c r="M2" s="76"/>
-      <c r="N2" s="76"/>
-    </row>
-    <row r="3" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="B2" s="66"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="66"/>
+      <c r="I2" s="66"/>
+      <c r="J2" s="66"/>
+      <c r="K2" s="66"/>
+      <c r="L2" s="66"/>
+      <c r="M2" s="66"/>
+      <c r="N2" s="66"/>
+    </row>
+    <row r="3" spans="1:15" ht="90" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>43</v>
       </c>
@@ -16562,14 +16635,14 @@
         <v>302</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
-      <c r="E4" s="66" t="s">
+      <c r="E4" s="64" t="s">
         <v>758</v>
       </c>
       <c r="F4" s="2" t="s">
@@ -16589,7 +16662,7 @@
       <c r="N4" s="2"/>
       <c r="O4" s="20"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="16" cm="1">
         <f t="array" aca="1" ref="A5" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>2</v>
@@ -16617,7 +16690,7 @@
       <c r="N5" s="2"/>
       <c r="O5" s="20"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="16" cm="1">
         <f t="array" aca="1" ref="A6" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>3</v>
@@ -16653,7 +16726,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="16" cm="1">
         <f t="array" aca="1" ref="A7" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>4</v>
@@ -16673,7 +16746,7 @@
       <c r="H7" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="I7" s="64" t="s">
+      <c r="I7" s="63" t="s">
         <v>756</v>
       </c>
       <c r="J7" s="2"/>
@@ -16685,7 +16758,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="16" cm="1">
         <f t="array" aca="1" ref="A8" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>5</v>
@@ -16695,7 +16768,7 @@
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
-      <c r="E8" s="63" t="s">
+      <c r="E8" s="2" t="s">
         <v>761</v>
       </c>
       <c r="F8" s="2" t="s">
@@ -16705,7 +16778,7 @@
       <c r="H8" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="I8" s="86" t="s">
+      <c r="I8" s="71" t="s">
         <v>304</v>
       </c>
       <c r="J8" s="20" t="s">
@@ -16719,7 +16792,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="16" cm="1">
         <f t="array" aca="1" ref="A9" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>6</v>
@@ -16729,7 +16802,7 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
-      <c r="E9" s="63" t="s">
+      <c r="E9" s="2" t="s">
         <v>762</v>
       </c>
       <c r="F9" s="2" t="s">
@@ -16739,7 +16812,7 @@
       <c r="H9" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="I9" s="86"/>
+      <c r="I9" s="71"/>
       <c r="J9" s="20" t="s">
         <v>62</v>
       </c>
@@ -16751,7 +16824,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="16" cm="1">
         <f t="array" aca="1" ref="A10" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>7</v>
@@ -16787,7 +16860,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="16" cm="1">
         <f t="array" aca="1" ref="A11" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>8</v>
@@ -16825,7 +16898,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="16" cm="1">
         <f t="array" aca="1" ref="A12" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>9</v>
@@ -16835,7 +16908,7 @@
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
-      <c r="E12" s="65" t="s">
+      <c r="E12" s="64" t="s">
         <v>767</v>
       </c>
       <c r="F12" s="2" t="s">
@@ -16845,7 +16918,7 @@
       <c r="H12" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="I12" s="86" t="s">
+      <c r="I12" s="71" t="s">
         <v>310</v>
       </c>
       <c r="J12" s="20" t="s">
@@ -16859,7 +16932,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="16" cm="1">
         <f t="array" aca="1" ref="A13" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>10</v>
@@ -16869,7 +16942,7 @@
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
-      <c r="E13" s="65" t="s">
+      <c r="E13" s="64" t="s">
         <v>768</v>
       </c>
       <c r="F13" s="2" t="s">
@@ -16879,7 +16952,7 @@
       <c r="H13" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="I13" s="86"/>
+      <c r="I13" s="71"/>
       <c r="J13" s="20" t="s">
         <v>62</v>
       </c>
@@ -16891,7 +16964,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="16" cm="1">
         <f t="array" aca="1" ref="A14" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>11</v>
@@ -16901,7 +16974,7 @@
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
-      <c r="E14" s="65" t="s">
+      <c r="E14" s="64" t="s">
         <v>769</v>
       </c>
       <c r="F14" s="2" t="s">
@@ -16911,7 +16984,7 @@
       <c r="H14" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="I14" s="86" t="s">
+      <c r="I14" s="71" t="s">
         <v>311</v>
       </c>
       <c r="J14" s="20" t="s">
@@ -16925,7 +16998,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="16" cm="1">
         <f t="array" aca="1" ref="A15" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>12</v>
@@ -16935,7 +17008,7 @@
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
-      <c r="E15" s="65" t="s">
+      <c r="E15" s="64" t="s">
         <v>770</v>
       </c>
       <c r="F15" s="2" t="s">
@@ -16945,7 +17018,7 @@
       <c r="H15" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="I15" s="86"/>
+      <c r="I15" s="71"/>
       <c r="J15" s="20" t="s">
         <v>62</v>
       </c>
@@ -16957,7 +17030,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="16" cm="1">
         <f t="array" aca="1" ref="A16" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>13</v>
@@ -16967,7 +17040,7 @@
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
-      <c r="E16" s="65" t="s">
+      <c r="E16" s="64" t="s">
         <v>764</v>
       </c>
       <c r="F16" s="2" t="s">
@@ -16977,7 +17050,7 @@
       <c r="H16" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="I16" s="86" t="s">
+      <c r="I16" s="71" t="s">
         <v>312</v>
       </c>
       <c r="J16" s="20" t="s">
@@ -16991,7 +17064,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="16" cm="1">
         <f t="array" aca="1" ref="A17" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>14</v>
@@ -17001,7 +17074,7 @@
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
-      <c r="E17" s="65" t="s">
+      <c r="E17" s="64" t="s">
         <v>765</v>
       </c>
       <c r="F17" s="2" t="s">
@@ -17011,7 +17084,7 @@
       <c r="H17" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="I17" s="86"/>
+      <c r="I17" s="71"/>
       <c r="J17" s="20" t="s">
         <v>62</v>
       </c>
@@ -17023,7 +17096,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="16" cm="1">
         <f t="array" aca="1" ref="A18" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>15</v>
@@ -17033,7 +17106,7 @@
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
-      <c r="E18" s="63" t="s">
+      <c r="E18" s="2" t="s">
         <v>360</v>
       </c>
       <c r="F18" s="2" t="s">
@@ -17061,7 +17134,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="16" cm="1">
         <f t="array" aca="1" ref="A19" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>16</v>
@@ -17095,7 +17168,7 @@
       <c r="N19" s="2"/>
       <c r="O19" s="20"/>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="16" cm="1">
         <f t="array" aca="1" ref="A20" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>17</v>
@@ -17105,7 +17178,7 @@
       </c>
       <c r="C20" s="22"/>
       <c r="D20" s="22"/>
-      <c r="E20" s="65" t="s">
+      <c r="E20" s="64" t="s">
         <v>72</v>
       </c>
       <c r="F20" s="2" t="s">
@@ -17121,43 +17194,43 @@
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A21" s="78" t="s">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A21" s="67" t="s">
         <v>316</v>
       </c>
-      <c r="B21" s="78"/>
-      <c r="C21" s="78"/>
-      <c r="D21" s="78"/>
-      <c r="E21" s="78"/>
-      <c r="F21" s="78"/>
-      <c r="G21" s="78"/>
-      <c r="H21" s="78"/>
-      <c r="I21" s="78"/>
-      <c r="J21" s="78"/>
-      <c r="K21" s="78"/>
-      <c r="L21" s="78"/>
-      <c r="M21" s="78"/>
-      <c r="N21" s="78"/>
-    </row>
-    <row r="22" spans="1:15" ht="18" x14ac:dyDescent="0.35">
-      <c r="A22" s="72" t="s">
+      <c r="B21" s="67"/>
+      <c r="C21" s="67"/>
+      <c r="D21" s="67"/>
+      <c r="E21" s="67"/>
+      <c r="F21" s="67"/>
+      <c r="G21" s="67"/>
+      <c r="H21" s="67"/>
+      <c r="I21" s="67"/>
+      <c r="J21" s="67"/>
+      <c r="K21" s="67"/>
+      <c r="L21" s="67"/>
+      <c r="M21" s="67"/>
+      <c r="N21" s="67"/>
+    </row>
+    <row r="22" spans="1:15" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A22" s="68" t="s">
         <v>90</v>
       </c>
-      <c r="B22" s="82"/>
-      <c r="C22" s="82"/>
-      <c r="D22" s="82"/>
-      <c r="E22" s="82"/>
-      <c r="F22" s="82"/>
-      <c r="G22" s="82"/>
-      <c r="H22" s="82"/>
-      <c r="I22" s="82"/>
-      <c r="J22" s="82"/>
-      <c r="K22" s="82"/>
-      <c r="L22" s="82"/>
-      <c r="M22" s="82"/>
-      <c r="N22" s="83"/>
-    </row>
-    <row r="23" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="B22" s="69"/>
+      <c r="C22" s="69"/>
+      <c r="D22" s="69"/>
+      <c r="E22" s="69"/>
+      <c r="F22" s="69"/>
+      <c r="G22" s="69"/>
+      <c r="H22" s="69"/>
+      <c r="I22" s="69"/>
+      <c r="J22" s="69"/>
+      <c r="K22" s="69"/>
+      <c r="L22" s="69"/>
+      <c r="M22" s="69"/>
+      <c r="N22" s="70"/>
+    </row>
+    <row r="23" spans="1:15" ht="90" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>43</v>
       </c>
@@ -17194,7 +17267,7 @@
       <c r="N23" s="25"/>
       <c r="O23" s="25"/>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="17">
         <v>1</v>
       </c>
@@ -17213,7 +17286,7 @@
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="16" cm="1">
         <f t="array" aca="1" ref="A25" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>2</v>
@@ -17237,7 +17310,7 @@
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="16" cm="1">
         <f t="array" aca="1" ref="A26" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>3</v>
@@ -17261,7 +17334,7 @@
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="16" cm="1">
         <f t="array" aca="1" ref="A27" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>4</v>
@@ -17269,7 +17342,7 @@
       <c r="B27" s="2"/>
       <c r="C27" s="22"/>
       <c r="D27" s="22"/>
-      <c r="E27" s="63" t="s">
+      <c r="E27" s="2" t="s">
         <v>776</v>
       </c>
       <c r="F27" s="2" t="s">
@@ -17285,7 +17358,7 @@
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="16" cm="1">
         <f t="array" aca="1" ref="A28" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>5</v>
@@ -17315,7 +17388,7 @@
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
     </row>
-    <row r="29" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="16" cm="1">
         <f t="array" aca="1" ref="A29" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>6</v>
@@ -17339,13 +17412,13 @@
       <c r="H29" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="I29" s="64" t="s">
+      <c r="I29" s="63" t="s">
         <v>756</v>
       </c>
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
     </row>
-    <row r="30" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="16" cm="1">
         <f t="array" aca="1" ref="A30" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>7</v>
@@ -17375,7 +17448,7 @@
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
     </row>
-    <row r="31" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" s="16" cm="1">
         <f t="array" aca="1" ref="A31" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>8</v>
@@ -17405,7 +17478,7 @@
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="16" cm="1">
         <f t="array" aca="1" ref="A32" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>9</v>
@@ -17433,7 +17506,7 @@
       <c r="J32" s="2"/>
       <c r="K32" s="2"/>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="16" cm="1">
         <f t="array" aca="1" ref="A33" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>10</v>
@@ -17463,7 +17536,7 @@
       <c r="J33" s="2"/>
       <c r="K33" s="2"/>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="16" cm="1">
         <f t="array" aca="1" ref="A34" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>11</v>
@@ -17477,7 +17550,7 @@
       <c r="D34" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="E34" s="63" t="s">
+      <c r="E34" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F34" s="2" t="s">
@@ -17493,7 +17566,7 @@
       <c r="J34" s="2"/>
       <c r="K34" s="2"/>
     </row>
-    <row r="35" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A35" s="16" cm="1">
         <f t="array" aca="1" ref="A35" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>12</v>
@@ -17523,7 +17596,7 @@
       <c r="J35" s="2"/>
       <c r="K35" s="2"/>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="16" cm="1">
         <f t="array" aca="1" ref="A36" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>13</v>
@@ -17537,7 +17610,7 @@
       <c r="D36" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="E36" s="63" t="s">
+      <c r="E36" s="2" t="s">
         <v>760</v>
       </c>
       <c r="F36" s="2" t="s">
@@ -17557,7 +17630,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="2" cm="1">
         <f t="array" aca="1" ref="A37" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>14</v>
@@ -17571,7 +17644,7 @@
       <c r="D37" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="E37" s="66" t="s">
+      <c r="E37" s="64" t="s">
         <v>781</v>
       </c>
       <c r="F37" s="2" t="s">
@@ -17584,7 +17657,7 @@
       <c r="J37" s="2"/>
       <c r="K37" s="2"/>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="16" cm="1">
         <f t="array" aca="1" ref="A38" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>15</v>
@@ -17612,7 +17685,7 @@
       <c r="J38" s="2"/>
       <c r="K38" s="2"/>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="16" cm="1">
         <f t="array" aca="1" ref="A39" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>16</v>
@@ -17626,7 +17699,7 @@
       <c r="D39" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="E39" s="65" t="s">
+      <c r="E39" s="64" t="s">
         <v>72</v>
       </c>
       <c r="F39" s="2" t="s">
@@ -17642,7 +17715,7 @@
       <c r="J39" s="2"/>
       <c r="K39" s="2"/>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="16" cm="1">
         <f t="array" aca="1" ref="A40" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>17</v>
@@ -17688,205 +17761,204 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B29C083E-476D-4A78-BA90-146F808CAD00}">
-  <dimension ref="A1:N24"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:R25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="26.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="39" customWidth="1"/>
-    <col min="6" max="6" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="64.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.109375" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="64.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.140625" customWidth="1"/>
     <col min="10" max="10" width="13" customWidth="1"/>
-    <col min="11" max="11" width="11.109375" customWidth="1"/>
-    <col min="12" max="12" width="18.44140625" customWidth="1"/>
+    <col min="11" max="11" width="11.140625" customWidth="1"/>
+    <col min="12" max="12" width="18.42578125" customWidth="1"/>
     <col min="13" max="13" width="20" customWidth="1"/>
-    <col min="14" max="14" width="18.6640625" customWidth="1"/>
+    <col min="14" max="14" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="76" t="s">
+    <row r="1" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="66" t="s">
         <v>328</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
-      <c r="H1" s="76"/>
-      <c r="I1" s="76"/>
-      <c r="J1" s="76"/>
-      <c r="K1" s="76"/>
-      <c r="L1" s="76"/>
-      <c r="M1" s="76"/>
-      <c r="N1" s="76"/>
-    </row>
-    <row r="2" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A2" s="76" t="s">
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="66"/>
+      <c r="H1" s="66"/>
+      <c r="I1" s="66"/>
+      <c r="J1" s="66"/>
+      <c r="K1" s="66"/>
+      <c r="L1" s="66"/>
+      <c r="M1" s="66"/>
+      <c r="N1" s="66"/>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="93" t="s">
+        <v>784</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>785</v>
+      </c>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="94"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="R2" s="20"/>
+    </row>
+    <row r="3" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A3" s="66" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="76"/>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
-      <c r="K2" s="76"/>
-      <c r="L2" s="76"/>
-      <c r="M2" s="76"/>
-      <c r="N2" s="76"/>
-    </row>
-    <row r="3" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
+      <c r="B3" s="66"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="66"/>
+      <c r="K3" s="66"/>
+      <c r="L3" s="66"/>
+      <c r="M3" s="66"/>
+      <c r="N3" s="66"/>
+    </row>
+    <row r="4" spans="1:18" ht="120" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B4" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C4" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D4" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E4" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F4" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G4" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H4" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I4" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J4" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K4" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="L4" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="M3" s="9" t="s">
+      <c r="M4" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="N3" s="9" t="s">
+      <c r="N4" s="9" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="17">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A5" s="17">
         <v>1</v>
       </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2" t="s">
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="G4" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="H4" s="38" t="s">
+      <c r="G5" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="H5" s="38" t="s">
         <v>329</v>
       </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="20" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A5" s="72" t="s">
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="20" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A6" s="68" t="s">
         <v>90</v>
       </c>
-      <c r="B5" s="82"/>
-      <c r="C5" s="82"/>
-      <c r="D5" s="82"/>
-      <c r="E5" s="82"/>
-      <c r="F5" s="82"/>
-      <c r="G5" s="82"/>
-      <c r="H5" s="82"/>
-      <c r="I5" s="82"/>
-      <c r="J5" s="82"/>
-      <c r="K5" s="82"/>
-      <c r="L5" s="82"/>
-      <c r="M5" s="82"/>
-      <c r="N5" s="83"/>
-    </row>
-    <row r="6" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
+      <c r="B6" s="69"/>
+      <c r="C6" s="69"/>
+      <c r="D6" s="69"/>
+      <c r="E6" s="69"/>
+      <c r="F6" s="69"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="69"/>
+      <c r="I6" s="69"/>
+      <c r="J6" s="69"/>
+      <c r="K6" s="69"/>
+      <c r="L6" s="69"/>
+      <c r="M6" s="69"/>
+      <c r="N6" s="70"/>
+    </row>
+    <row r="7" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B7" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C7" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D7" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E7" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F7" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="G7" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H7" s="5" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="22">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A8" s="22">
         <v>1</v>
       </c>
-      <c r="B7" s="34"/>
-      <c r="C7" s="34"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3" t="s">
+      <c r="B8" s="34"/>
+      <c r="C8" s="34"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3" t="s">
         <v>317</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G7" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="16" cm="1">
-        <f t="array" aca="1" ref="A8" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>2</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="C8" s="22"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="2" t="s">
-        <v>96</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>61</v>
@@ -17895,13 +17967,13 @@
         <v>62</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="16" cm="1">
         <f t="array" aca="1" ref="A9" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>319</v>
@@ -17909,22 +17981,22 @@
       <c r="C9" s="22"/>
       <c r="D9" s="22"/>
       <c r="E9" s="2" t="s">
-        <v>60</v>
+        <v>96</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="G9" s="20" t="s">
+      <c r="G9" s="21" t="s">
         <v>62</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="16" cm="1">
         <f t="array" aca="1" ref="A10" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>319</v>
@@ -17932,22 +18004,22 @@
       <c r="C10" s="22"/>
       <c r="D10" s="22"/>
       <c r="E10" s="2" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="G10" s="20" t="s">
         <v>62</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="16" cm="1">
         <f t="array" aca="1" ref="A11" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>319</v>
@@ -17955,22 +18027,22 @@
       <c r="C11" s="22"/>
       <c r="D11" s="22"/>
       <c r="E11" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="G11" s="20" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="16" cm="1">
         <f t="array" aca="1" ref="A12" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>319</v>
@@ -17978,22 +18050,22 @@
       <c r="C12" s="22"/>
       <c r="D12" s="22"/>
       <c r="E12" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G12" s="20" t="s">
         <v>64</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="16" cm="1">
         <f t="array" aca="1" ref="A13" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>319</v>
@@ -18001,22 +18073,22 @@
       <c r="C13" s="22"/>
       <c r="D13" s="22"/>
       <c r="E13" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="G13" s="20" t="s">
         <v>64</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="16" cm="1">
         <f t="array" aca="1" ref="A14" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>319</v>
@@ -18024,7 +18096,7 @@
       <c r="C14" s="22"/>
       <c r="D14" s="22"/>
       <c r="E14" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>61</v>
@@ -18033,13 +18105,13 @@
         <v>64</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="16" cm="1">
         <f t="array" aca="1" ref="A15" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>319</v>
@@ -18047,7 +18119,7 @@
       <c r="C15" s="22"/>
       <c r="D15" s="22"/>
       <c r="E15" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>61</v>
@@ -18056,13 +18128,13 @@
         <v>64</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="16" cm="1">
         <f t="array" aca="1" ref="A16" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>319</v>
@@ -18070,20 +18142,22 @@
       <c r="C16" s="22"/>
       <c r="D16" s="22"/>
       <c r="E16" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G16" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="H16" s="3"/>
-    </row>
-    <row r="17" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="H16" s="3" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="16" cm="1">
         <f t="array" aca="1" ref="A17" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>319</v>
@@ -18091,22 +18165,20 @@
       <c r="C17" s="22"/>
       <c r="D17" s="22"/>
       <c r="E17" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="G17" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="H17" s="3"/>
+    </row>
+    <row r="18" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="16" cm="1">
         <f t="array" aca="1" ref="A18" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>319</v>
@@ -18114,22 +18186,22 @@
       <c r="C18" s="22"/>
       <c r="D18" s="22"/>
       <c r="E18" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="G18" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="H18" s="39" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="H18" s="3" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="16" cm="1">
         <f t="array" aca="1" ref="A19" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>319</v>
@@ -18137,7 +18209,7 @@
       <c r="C19" s="22"/>
       <c r="D19" s="22"/>
       <c r="E19" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>61</v>
@@ -18146,13 +18218,13 @@
         <v>64</v>
       </c>
       <c r="H19" s="39" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="16" cm="1">
         <f t="array" aca="1" ref="A20" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>319</v>
@@ -18160,116 +18232,139 @@
       <c r="C20" s="22"/>
       <c r="D20" s="22"/>
       <c r="E20" s="2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="G20" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="H20" s="3"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H20" s="39" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="16" cm="1">
         <f t="array" aca="1" ref="A21" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>15</v>
-      </c>
-      <c r="B21" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>319</v>
+      </c>
       <c r="C21" s="22"/>
       <c r="D21" s="22"/>
       <c r="E21" s="2" t="s">
-        <v>336</v>
+        <v>89</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="H21" s="39" t="s">
-        <v>337</v>
-      </c>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-    </row>
-    <row r="22" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="G21" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="H21" s="3"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="16" cm="1">
         <f t="array" aca="1" ref="A22" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>16</v>
-      </c>
-      <c r="B22" s="34" t="s">
-        <v>326</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="F22" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" s="2"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="F22" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="G22" s="21" t="s">
-        <v>64</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="G22" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H22" s="39" t="s">
+        <v>337</v>
+      </c>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+    </row>
+    <row r="23" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="16" cm="1">
         <f t="array" aca="1" ref="A23" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>17</v>
-      </c>
-      <c r="B23" s="45"/>
-      <c r="C23" s="45"/>
-      <c r="D23" s="45"/>
-      <c r="E23" s="46" t="s">
-        <v>98</v>
-      </c>
-      <c r="F23" s="45" t="s">
-        <v>22</v>
-      </c>
-      <c r="G23" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="H23" s="45" t="s">
-        <v>339</v>
-      </c>
-      <c r="I23" s="45"/>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="B23" s="34" t="s">
+        <v>326</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G23" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" s="4" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="16" cm="1">
         <f t="array" aca="1" ref="A24" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
+        <v>17</v>
+      </c>
+      <c r="B24" s="45"/>
+      <c r="C24" s="45"/>
+      <c r="D24" s="45"/>
+      <c r="E24" s="46" t="s">
+        <v>98</v>
+      </c>
+      <c r="F24" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="G24" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="H24" s="45" t="s">
+        <v>339</v>
+      </c>
+      <c r="I24" s="45"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="16" cm="1">
+        <f t="array" aca="1" ref="A25" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>18</v>
       </c>
-      <c r="B24" s="2"/>
-      <c r="C24" s="22"/>
-      <c r="D24" s="22"/>
-      <c r="E24" s="2" t="s">
+      <c r="B25" s="2"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="F24" s="2" t="s">
+      <c r="F25" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="G24" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="H24" s="39" t="s">
+      <c r="G25" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="H25" s="39" t="s">
         <v>337</v>
       </c>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:N1"/>
-    <mergeCell ref="A2:N2"/>
-    <mergeCell ref="A5:N5"/>
+    <mergeCell ref="A3:N3"/>
+    <mergeCell ref="A6:N6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -18282,6 +18377,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009FF49975E8DE8E439848F855486C4ED8" ma:contentTypeVersion="6" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f39b8ea50b4efafd019d975ed3685cf0">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4351ea0b-59b6-4bb2-9550-55596f432c66" xmlns:ns3="abb7c066-0e75-4f9f-a7fd-256dceefbfe6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6a7f805c69beeed54a184edbcd84b07f" ns2:_="" ns3:_="">
     <xsd:import namespace="4351ea0b-59b6-4bb2-9550-55596f432c66"/>
@@ -18458,15 +18562,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{632DF58F-9925-4F24-8594-A7A2396951DC}">
   <ds:schemaRefs>
@@ -18485,13 +18580,28 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{865B90D8-3BD5-4E56-9796-04F4803D2A05}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7589AAA9-D219-4D8F-8882-A5AE3E5367AE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7589AAA9-D219-4D8F-8882-A5AE3E5367AE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{865B90D8-3BD5-4E56-9796-04F4803D2A05}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="4351ea0b-59b6-4bb2-9550-55596f432c66"/>
+    <ds:schemaRef ds:uri="abb7c066-0e75-4f9f-a7fd-256dceefbfe6"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
